--- a/artfynd/A 61382-2025 artfynd.xlsx
+++ b/artfynd/A 61382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130734182</v>
+        <v>130741286</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443903</v>
+        <v>443968</v>
       </c>
       <c r="R2" t="n">
-        <v>7053286</v>
+        <v>7052990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +766,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog.</t>
+          <t>Avbarkade en något klen gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,44 +775,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -937,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130741286</v>
+        <v>130734182</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,50 +935,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443968</v>
+        <v>443903</v>
       </c>
       <c r="R4" t="n">
-        <v>7052990</v>
+        <v>7053286</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,7 +1002,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Avbarkade en något klen gran</t>
+          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,28 +1011,54 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130734193</v>
+        <v>130734153</v>
       </c>
       <c r="B5" t="n">
-        <v>79211</v>
+        <v>91757</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,26 +1066,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1093,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444436</v>
+        <v>443857</v>
       </c>
       <c r="R5" t="n">
-        <v>7053798</v>
+        <v>7053224</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,6 +1135,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i stambasen av en stående grov gran med 50 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1148,7 +1157,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
+          <t>Flerskiktad äldre granskog med inslag av björk och enstaka asp.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1163,12 +1172,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1186,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130734153</v>
+        <v>130734193</v>
       </c>
       <c r="B6" t="n">
-        <v>91757</v>
+        <v>79211</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,30 +1206,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1228,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443857</v>
+        <v>444436</v>
       </c>
       <c r="R6" t="n">
-        <v>7053224</v>
+        <v>7053798</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,11 +1271,6 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i stambasen av en stående grov gran med 50 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Flerskiktad äldre granskog med inslag av björk och enstaka asp.</t>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1559,7 +1559,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130741291</v>
+        <v>130741302</v>
       </c>
       <c r="B9" t="n">
         <v>57854</v>
@@ -1594,10 +1594,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443794</v>
+        <v>443997</v>
       </c>
       <c r="R9" t="n">
-        <v>7053002</v>
+        <v>7053008</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,7 +1634,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,10 +1661,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130734156</v>
+        <v>130741291</v>
       </c>
       <c r="B10" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,37 +1672,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443886</v>
+        <v>443794</v>
       </c>
       <c r="R10" t="n">
-        <v>7053279</v>
+        <v>7053002</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1739,7 +1736,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en granhögstubbe.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,44 +1745,18 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1932,10 +1903,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130741302</v>
+        <v>130734156</v>
       </c>
       <c r="B12" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1943,34 +1914,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443997</v>
+        <v>443886</v>
       </c>
       <c r="R12" t="n">
-        <v>7053008</v>
+        <v>7053279</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2007,7 +1981,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Gott om fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2016,28 +1990,54 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130741279</v>
+        <v>130741320</v>
       </c>
       <c r="B13" t="n">
-        <v>57854</v>
+        <v>89155</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,21 +2045,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444007</v>
+        <v>444326</v>
       </c>
       <c r="R13" t="n">
-        <v>7053457</v>
+        <v>7053588</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2105,11 +2105,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2136,10 +2131,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130741320</v>
+        <v>130741279</v>
       </c>
       <c r="B14" t="n">
-        <v>89155</v>
+        <v>57854</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2147,21 +2142,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2171,10 +2166,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444326</v>
+        <v>444007</v>
       </c>
       <c r="R14" t="n">
-        <v>7053588</v>
+        <v>7053457</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,6 +2202,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2723,10 +2723,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130741284</v>
+        <v>130734190</v>
       </c>
       <c r="B19" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2734,34 +2734,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443929</v>
+        <v>444347</v>
       </c>
       <c r="R19" t="n">
-        <v>7052944</v>
+        <v>7053668</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2798,7 +2801,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Garnlav på en stående död gran med full längd och ca 10-20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2807,25 +2810,56 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130734190</v>
+        <v>130734177</v>
       </c>
       <c r="B20" t="n">
         <v>79211</v>
@@ -2863,10 +2897,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444347</v>
+        <v>443938</v>
       </c>
       <c r="R20" t="n">
-        <v>7053668</v>
+        <v>7053186</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2903,7 +2937,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Garnlav på en stående död gran med full längd och ca 10-20 cm i brösthöjdsdiameter.</t>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2921,11 +2955,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2938,12 +2967,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2961,7 +2990,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130734177</v>
+        <v>130734192</v>
       </c>
       <c r="B21" t="n">
         <v>79211</v>
@@ -2999,10 +3028,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>443938</v>
+        <v>444423</v>
       </c>
       <c r="R21" t="n">
-        <v>7053186</v>
+        <v>7053773</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3039,7 +3068,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog.</t>
+          <t>Måttligt till rikligt med garnlavsbålar på flera granar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3055,6 +3084,11 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3092,10 +3126,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130734192</v>
+        <v>130741284</v>
       </c>
       <c r="B22" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3103,37 +3137,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444423</v>
+        <v>443929</v>
       </c>
       <c r="R22" t="n">
-        <v>7053773</v>
+        <v>7052944</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3170,7 +3201,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt med garnlavsbålar på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3179,49 +3210,18 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3432,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130734162</v>
+        <v>130741297</v>
       </c>
       <c r="B25" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3443,37 +3443,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444375</v>
+        <v>443871</v>
       </c>
       <c r="R25" t="n">
-        <v>7054118</v>
+        <v>7052942</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3508,50 +3505,29 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3698,7 +3674,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130734165</v>
+        <v>130734162</v>
       </c>
       <c r="B27" t="n">
         <v>79211</v>
@@ -3736,10 +3712,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444343</v>
+        <v>444375</v>
       </c>
       <c r="R27" t="n">
-        <v>7054057</v>
+        <v>7054118</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3772,11 +3748,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3829,10 +3800,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130734185</v>
+        <v>130741314</v>
       </c>
       <c r="B28" t="n">
-        <v>79211</v>
+        <v>91781</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3840,37 +3811,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444157</v>
+        <v>444416</v>
       </c>
       <c r="R28" t="n">
-        <v>7053507</v>
+        <v>7053728</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3905,65 +3869,34 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130741314</v>
+        <v>130734165</v>
       </c>
       <c r="B29" t="n">
-        <v>91781</v>
+        <v>79211</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3971,30 +3904,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444416</v>
+        <v>444343</v>
       </c>
       <c r="R29" t="n">
-        <v>7053728</v>
+        <v>7054057</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4029,34 +3969,65 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130741297</v>
+        <v>130734185</v>
       </c>
       <c r="B30" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4064,34 +4035,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443871</v>
+        <v>444157</v>
       </c>
       <c r="R30" t="n">
-        <v>7052942</v>
+        <v>7053507</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4128,7 +4102,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4137,28 +4111,54 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130741313</v>
+        <v>130741290</v>
       </c>
       <c r="B31" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4166,30 +4166,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443985</v>
+        <v>444005</v>
       </c>
       <c r="R31" t="n">
-        <v>7052983</v>
+        <v>7053074</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4222,6 +4234,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bohål ca 3 m upp i granhögstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4248,10 +4265,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130741290</v>
+        <v>130734181</v>
       </c>
       <c r="B32" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4259,42 +4276,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444005</v>
+        <v>443859</v>
       </c>
       <c r="R32" t="n">
-        <v>7053074</v>
+        <v>7053310</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4331,7 +4343,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Bohål ca 3 m upp i granhögstubbe</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4340,25 +4352,51 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130734181</v>
+        <v>130734178</v>
       </c>
       <c r="B33" t="n">
         <v>79211</v>
@@ -4396,10 +4434,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443859</v>
+        <v>443988</v>
       </c>
       <c r="R33" t="n">
-        <v>7053310</v>
+        <v>7053189</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4436,7 +4474,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>På gammal gran i luckig äldre granskog.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4489,10 +4527,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130734178</v>
+        <v>130741313</v>
       </c>
       <c r="B34" t="n">
-        <v>79211</v>
+        <v>91781</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4500,37 +4538,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443988</v>
+        <v>443985</v>
       </c>
       <c r="R34" t="n">
-        <v>7053189</v>
+        <v>7052983</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4565,55 +4596,24 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gammal gran i luckig äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -5319,10 +5319,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130741301</v>
+        <v>130734173</v>
       </c>
       <c r="B41" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5330,34 +5330,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443990</v>
+        <v>444046</v>
       </c>
       <c r="R41" t="n">
-        <v>7052974</v>
+        <v>7053496</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5394,7 +5397,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På grenar av en stående död gran med full längd och 36 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5403,25 +5406,51 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130741295</v>
+        <v>130741292</v>
       </c>
       <c r="B42" t="n">
         <v>57854</v>
@@ -5456,10 +5485,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443845</v>
+        <v>443750</v>
       </c>
       <c r="R42" t="n">
-        <v>7052918</v>
+        <v>7052993</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5496,7 +5525,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5523,7 +5552,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130741292</v>
+        <v>130741301</v>
       </c>
       <c r="B43" t="n">
         <v>57854</v>
@@ -5558,10 +5587,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443750</v>
+        <v>443990</v>
       </c>
       <c r="R43" t="n">
-        <v>7052993</v>
+        <v>7052974</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5598,7 +5627,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5625,7 +5654,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130734144</v>
+        <v>130741295</v>
       </c>
       <c r="B44" t="n">
         <v>57854</v>
@@ -5654,24 +5683,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444016</v>
+        <v>443845</v>
       </c>
       <c r="R44" t="n">
-        <v>7053579</v>
+        <v>7052918</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5708,7 +5729,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5719,51 +5740,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130734173</v>
+        <v>130734144</v>
       </c>
       <c r="B45" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5771,26 +5767,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5798,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444046</v>
+        <v>444016</v>
       </c>
       <c r="R45" t="n">
-        <v>7053496</v>
+        <v>7053579</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5838,7 +5839,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På grenar av en stående död gran med full längd och 36 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5847,7 +5848,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5891,7 +5891,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130741281</v>
+        <v>130734147</v>
       </c>
       <c r="B46" t="n">
         <v>57854</v>
@@ -5920,16 +5920,24 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443901</v>
+        <v>443820</v>
       </c>
       <c r="R46" t="n">
-        <v>7053024</v>
+        <v>7053223</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5966,7 +5974,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska, i god mängd längs minst 6 meter på en granstam inom en avverkningsanmäld yta och utanför planerad naturhänsyn.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5977,23 +5985,53 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI46" t="inlineStr">
+        <is>
+          <t>Flerakiktad äldre granskog med björk och inslag av asp. Stor stamdiameterspridning med naturvärdes-granar med över 50 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130734147</v>
+        <v>130741281</v>
       </c>
       <c r="B47" t="n">
         <v>57854</v>
@@ -6022,24 +6060,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443820</v>
+        <v>443901</v>
       </c>
       <c r="R47" t="n">
-        <v>7053223</v>
+        <v>7053024</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6076,7 +6106,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, färska, i god mängd längs minst 6 meter på en granstam inom en avverkningsanmäld yta och utanför planerad naturhänsyn.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6087,46 +6117,16 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Flerakiktad äldre granskog med björk och inslag av asp. Stor stamdiameterspridning med naturvärdes-granar med över 50 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6264,7 +6264,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130741299</v>
+        <v>130741288</v>
       </c>
       <c r="B49" t="n">
         <v>57854</v>
@@ -6299,10 +6299,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443972</v>
+        <v>443996</v>
       </c>
       <c r="R49" t="n">
-        <v>7052967</v>
+        <v>7053048</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6339,7 +6339,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6366,7 +6366,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130741288</v>
+        <v>130741299</v>
       </c>
       <c r="B50" t="n">
         <v>57854</v>
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443996</v>
+        <v>443972</v>
       </c>
       <c r="R50" t="n">
-        <v>7053048</v>
+        <v>7052967</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6441,7 +6441,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6840,10 +6840,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130741311</v>
+        <v>130734167</v>
       </c>
       <c r="B54" t="n">
-        <v>91781</v>
+        <v>79211</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6851,30 +6851,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443991</v>
+        <v>444319</v>
       </c>
       <c r="R54" t="n">
-        <v>7052955</v>
+        <v>7054017</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6909,34 +6916,65 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130741316</v>
+        <v>130741311</v>
       </c>
       <c r="B55" t="n">
-        <v>79211</v>
+        <v>91781</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6944,23 +6982,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6968,10 +7002,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444000</v>
+        <v>443991</v>
       </c>
       <c r="R55" t="n">
-        <v>7053558</v>
+        <v>7052955</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7004,11 +7038,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7035,7 +7064,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130734167</v>
+        <v>130741316</v>
       </c>
       <c r="B56" t="n">
         <v>79211</v>
@@ -7064,19 +7093,16 @@
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444319</v>
+        <v>444000</v>
       </c>
       <c r="R56" t="n">
-        <v>7054017</v>
+        <v>7053558</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7113,7 +7139,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7122,54 +7148,28 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130734171</v>
+        <v>130741287</v>
       </c>
       <c r="B57" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7177,37 +7177,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443981</v>
+        <v>444000</v>
       </c>
       <c r="R57" t="n">
-        <v>7053488</v>
+        <v>7053028</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7244,7 +7241,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7253,54 +7250,28 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130741310</v>
+        <v>130741298</v>
       </c>
       <c r="B58" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7308,19 +7279,23 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7328,10 +7303,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443891</v>
+        <v>443946</v>
       </c>
       <c r="R58" t="n">
-        <v>7053029</v>
+        <v>7052921</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7364,6 +7339,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7390,10 +7370,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130741298</v>
+        <v>130741310</v>
       </c>
       <c r="B59" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7401,23 +7381,19 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
@@ -7425,10 +7401,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443946</v>
+        <v>443891</v>
       </c>
       <c r="R59" t="n">
-        <v>7052921</v>
+        <v>7053029</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7461,11 +7437,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7585,10 +7556,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130741287</v>
+        <v>130734171</v>
       </c>
       <c r="B61" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7596,34 +7567,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444000</v>
+        <v>443981</v>
       </c>
       <c r="R61" t="n">
-        <v>7053028</v>
+        <v>7053488</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7660,7 +7634,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7669,28 +7643,54 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130741308</v>
+        <v>130734155</v>
       </c>
       <c r="B62" t="n">
-        <v>91781</v>
+        <v>91757</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7698,30 +7698,41 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444020</v>
+        <v>443861</v>
       </c>
       <c r="R62" t="n">
-        <v>7053458</v>
+        <v>7053306</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7756,24 +7767,55 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i stambasen av en levande relativt grov gran.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7882,10 +7924,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130734155</v>
+        <v>130741308</v>
       </c>
       <c r="B64" t="n">
-        <v>91757</v>
+        <v>91781</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7893,41 +7935,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443861</v>
+        <v>444020</v>
       </c>
       <c r="R64" t="n">
-        <v>7053306</v>
+        <v>7053458</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7962,55 +7993,24 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i stambasen av en levande relativt grov gran.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130734184</v>
+        <v>130734151</v>
       </c>
       <c r="B68" t="n">
-        <v>79211</v>
+        <v>80317</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8382,21 +8382,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8409,10 +8409,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444032</v>
+        <v>444218</v>
       </c>
       <c r="R68" t="n">
-        <v>7053290</v>
+        <v>7053557</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8449,7 +8449,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Garnlav på en tydligt gammal gran i gles senvuxen granskog.</t>
+          <t>Växer på en levande skadad sälg.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8467,24 +8467,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI68" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av björk och enstaka sälg.</t>
+        </is>
+      </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8502,7 +8507,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130734188</v>
+        <v>130734184</v>
       </c>
       <c r="B69" t="n">
         <v>79211</v>
@@ -8540,10 +8545,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444304</v>
+        <v>444032</v>
       </c>
       <c r="R69" t="n">
-        <v>7053564</v>
+        <v>7053290</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8580,7 +8585,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Växer på en tydligt gammal gran i relativt senvuxen gles granskog.</t>
+          <t>Garnlav på en tydligt gammal gran i gles senvuxen granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8633,7 +8638,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130734191</v>
+        <v>130734188</v>
       </c>
       <c r="B70" t="n">
         <v>79211</v>
@@ -8671,10 +8676,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444407</v>
+        <v>444304</v>
       </c>
       <c r="R70" t="n">
-        <v>7053726</v>
+        <v>7053564</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8711,7 +8716,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på gran.</t>
+          <t>Växer på en tydligt gammal gran i relativt senvuxen gles granskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8727,11 +8732,6 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -8769,7 +8769,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130734168</v>
+        <v>130734191</v>
       </c>
       <c r="B71" t="n">
         <v>79211</v>
@@ -8807,10 +8807,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444293</v>
+        <v>444407</v>
       </c>
       <c r="R71" t="n">
-        <v>7054016</v>
+        <v>7053726</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8845,6 +8845,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med garnlav på gran.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8858,6 +8863,11 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -8895,10 +8905,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130734151</v>
+        <v>130734168</v>
       </c>
       <c r="B72" t="n">
-        <v>80317</v>
+        <v>79211</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8906,21 +8916,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8933,10 +8943,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444218</v>
+        <v>444293</v>
       </c>
       <c r="R72" t="n">
-        <v>7053557</v>
+        <v>7054016</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8971,11 +8981,6 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Växer på en levande skadad sälg.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8991,29 +8996,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med inslag av björk och enstaka sälg.</t>
-        </is>
-      </c>
       <c r="AJ72" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK72" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>

--- a/artfynd/A 61382-2025 artfynd.xlsx
+++ b/artfynd/A 61382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130741286</v>
+        <v>130734182</v>
       </c>
       <c r="B2" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,50 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443968</v>
+        <v>443903</v>
       </c>
       <c r="R2" t="n">
-        <v>7052990</v>
+        <v>7053286</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Avbarkade en något klen gran</t>
+          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,18 +762,44 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -924,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130734182</v>
+        <v>130741286</v>
       </c>
       <c r="B4" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,37 +948,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443903</v>
+        <v>443968</v>
       </c>
       <c r="R4" t="n">
-        <v>7053286</v>
+        <v>7052990</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1028,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog.</t>
+          <t>Avbarkade en något klen gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,44 +1037,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1559,10 +1559,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130741302</v>
+        <v>130734156</v>
       </c>
       <c r="B9" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,34 +1570,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443997</v>
+        <v>443886</v>
       </c>
       <c r="R9" t="n">
-        <v>7053008</v>
+        <v>7053279</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,7 +1637,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Gott om fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,25 +1646,51 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130741291</v>
+        <v>130741302</v>
       </c>
       <c r="B10" t="n">
         <v>57854</v>
@@ -1696,10 +1725,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443794</v>
+        <v>443997</v>
       </c>
       <c r="R10" t="n">
-        <v>7053002</v>
+        <v>7053008</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1736,7 +1765,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1763,7 +1792,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130734145</v>
+        <v>130741291</v>
       </c>
       <c r="B11" t="n">
         <v>57854</v>
@@ -1792,24 +1821,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443967</v>
+        <v>443794</v>
       </c>
       <c r="R11" t="n">
-        <v>7053469</v>
+        <v>7053002</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1846,7 +1867,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,56 +1878,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog.</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130734156</v>
+        <v>130734145</v>
       </c>
       <c r="B12" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,24 +1905,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1941,10 +1937,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443886</v>
+        <v>443967</v>
       </c>
       <c r="R12" t="n">
-        <v>7053279</v>
+        <v>7053469</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1981,7 +1977,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en granhögstubbe.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1990,7 +1986,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1999,6 +1994,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130741279</v>
+        <v>130734180</v>
       </c>
       <c r="B14" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,34 +2142,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444007</v>
+        <v>443846</v>
       </c>
       <c r="R14" t="n">
-        <v>7053457</v>
+        <v>7053252</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2206,7 +2209,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Växer på grenar av en stående död gran med full längd (bhd ca 30 cm).</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2215,25 +2218,51 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130734180</v>
+        <v>130734170</v>
       </c>
       <c r="B15" t="n">
         <v>79211</v>
@@ -2271,10 +2300,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443846</v>
+        <v>444133</v>
       </c>
       <c r="R15" t="n">
-        <v>7053252</v>
+        <v>7053693</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2309,11 +2338,6 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Växer på grenar av en stående död gran med full längd (bhd ca 30 cm).</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2341,12 +2365,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2364,7 +2388,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130734170</v>
+        <v>130734164</v>
       </c>
       <c r="B16" t="n">
         <v>79211</v>
@@ -2402,10 +2426,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444133</v>
+        <v>444362</v>
       </c>
       <c r="R16" t="n">
-        <v>7053693</v>
+        <v>7054079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2438,6 +2462,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På gamla granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2490,10 +2519,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130734164</v>
+        <v>130741279</v>
       </c>
       <c r="B17" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2501,37 +2530,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444362</v>
+        <v>444007</v>
       </c>
       <c r="R17" t="n">
-        <v>7054079</v>
+        <v>7053457</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2568,7 +2594,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gamla granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2577,44 +2603,18 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130741282</v>
+        <v>130734150</v>
       </c>
       <c r="B23" t="n">
-        <v>57854</v>
+        <v>80317</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,34 +3239,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443897</v>
+        <v>444358</v>
       </c>
       <c r="R23" t="n">
-        <v>7052981</v>
+        <v>7054049</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3303,7 +3310,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Gott om bålar av skrovellav på en hyfsat grov sälg.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3312,28 +3319,59 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med björk och inslag av sälg.</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130741285</v>
+        <v>130734162</v>
       </c>
       <c r="B24" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3341,34 +3379,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443963</v>
+        <v>444375</v>
       </c>
       <c r="R24" t="n">
-        <v>7052972</v>
+        <v>7054118</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3403,39 +3444,60 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130741297</v>
+        <v>130741314</v>
       </c>
       <c r="B25" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3443,23 +3505,19 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3467,10 +3525,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443871</v>
+        <v>444416</v>
       </c>
       <c r="R25" t="n">
-        <v>7052942</v>
+        <v>7053728</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3503,11 +3561,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3534,10 +3587,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130734150</v>
+        <v>130734165</v>
       </c>
       <c r="B26" t="n">
-        <v>80317</v>
+        <v>79211</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3545,30 +3598,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3576,10 +3625,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444358</v>
+        <v>444343</v>
       </c>
       <c r="R26" t="n">
-        <v>7054049</v>
+        <v>7054057</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3616,7 +3665,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gott om bålar av skrovellav på en hyfsat grov sälg.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3634,29 +3683,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med björk och inslag av sälg.</t>
-        </is>
-      </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3674,7 +3718,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130734162</v>
+        <v>130734185</v>
       </c>
       <c r="B27" t="n">
         <v>79211</v>
@@ -3712,10 +3756,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444375</v>
+        <v>444157</v>
       </c>
       <c r="R27" t="n">
-        <v>7054118</v>
+        <v>7053507</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3748,6 +3792,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3800,10 +3849,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130741314</v>
+        <v>130741297</v>
       </c>
       <c r="B28" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3811,19 +3860,23 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3831,10 +3884,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444416</v>
+        <v>443871</v>
       </c>
       <c r="R28" t="n">
-        <v>7053728</v>
+        <v>7052942</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3867,6 +3920,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3893,10 +3951,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130734165</v>
+        <v>130741282</v>
       </c>
       <c r="B29" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3904,37 +3962,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444343</v>
+        <v>443897</v>
       </c>
       <c r="R29" t="n">
-        <v>7054057</v>
+        <v>7052981</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3971,7 +4026,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3980,54 +4035,28 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130734185</v>
+        <v>130741285</v>
       </c>
       <c r="B30" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4035,37 +4064,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444157</v>
+        <v>443963</v>
       </c>
       <c r="R30" t="n">
-        <v>7053507</v>
+        <v>7052972</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4102,7 +4128,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4111,54 +4137,28 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130741290</v>
+        <v>130734181</v>
       </c>
       <c r="B31" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4166,42 +4166,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444005</v>
+        <v>443859</v>
       </c>
       <c r="R31" t="n">
-        <v>7053074</v>
+        <v>7053310</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4238,7 +4233,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Bohål ca 3 m upp i granhögstubbe</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4247,25 +4242,51 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130734181</v>
+        <v>130734178</v>
       </c>
       <c r="B32" t="n">
         <v>79211</v>
@@ -4303,10 +4324,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443859</v>
+        <v>443988</v>
       </c>
       <c r="R32" t="n">
-        <v>7053310</v>
+        <v>7053189</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4343,7 +4364,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>På gammal gran i luckig äldre granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4396,10 +4417,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130734178</v>
+        <v>130741313</v>
       </c>
       <c r="B33" t="n">
-        <v>79211</v>
+        <v>91781</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4407,37 +4428,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443988</v>
+        <v>443985</v>
       </c>
       <c r="R33" t="n">
-        <v>7053189</v>
+        <v>7052983</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4472,65 +4486,34 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gammal gran i luckig äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130741313</v>
+        <v>130741290</v>
       </c>
       <c r="B34" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4538,30 +4521,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443985</v>
+        <v>444005</v>
       </c>
       <c r="R34" t="n">
-        <v>7052983</v>
+        <v>7053074</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4594,6 +4589,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Bohål ca 3 m upp i granhögstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4620,10 +4620,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130741289</v>
+        <v>130734189</v>
       </c>
       <c r="B35" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4631,34 +4631,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>443999</v>
+        <v>444342</v>
       </c>
       <c r="R35" t="n">
-        <v>7053066</v>
+        <v>7053646</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4695,7 +4698,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Relativt rikligt med garnlavsbålar på gran.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4704,28 +4707,59 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130741294</v>
+        <v>130734176</v>
       </c>
       <c r="B36" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4733,34 +4767,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>443835</v>
+        <v>444149</v>
       </c>
       <c r="R36" t="n">
-        <v>7052933</v>
+        <v>7053319</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4797,7 +4834,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På gran i gles äldre granskog.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4806,18 +4843,44 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4955,10 +5018,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130734189</v>
+        <v>130741289</v>
       </c>
       <c r="B38" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4966,37 +5029,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>444342</v>
+        <v>443999</v>
       </c>
       <c r="R38" t="n">
-        <v>7053646</v>
+        <v>7053066</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5033,7 +5093,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlavsbålar på gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5042,59 +5102,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130734176</v>
+        <v>130741294</v>
       </c>
       <c r="B39" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5102,37 +5131,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>444149</v>
+        <v>443835</v>
       </c>
       <c r="R39" t="n">
-        <v>7053319</v>
+        <v>7052933</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5169,7 +5195,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>På gran i gles äldre granskog.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5178,44 +5204,18 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -6738,10 +6738,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130741293</v>
+        <v>130734167</v>
       </c>
       <c r="B53" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6749,34 +6749,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443827</v>
+        <v>444319</v>
       </c>
       <c r="R53" t="n">
-        <v>7052932</v>
+        <v>7054017</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6813,7 +6816,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6822,28 +6825,54 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130734167</v>
+        <v>130741311</v>
       </c>
       <c r="B54" t="n">
-        <v>79211</v>
+        <v>91781</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6851,37 +6880,30 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444319</v>
+        <v>443991</v>
       </c>
       <c r="R54" t="n">
-        <v>7054017</v>
+        <v>7052955</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6916,65 +6938,34 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130741311</v>
+        <v>130741316</v>
       </c>
       <c r="B55" t="n">
-        <v>91781</v>
+        <v>79211</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6982,19 +6973,23 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7002,10 +6997,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443991</v>
+        <v>444000</v>
       </c>
       <c r="R55" t="n">
-        <v>7052955</v>
+        <v>7053558</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7038,6 +7033,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7064,10 +7064,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130741316</v>
+        <v>130741293</v>
       </c>
       <c r="B56" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7075,21 +7075,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>444000</v>
+        <v>443827</v>
       </c>
       <c r="R56" t="n">
-        <v>7053558</v>
+        <v>7052932</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7166,10 +7166,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130741287</v>
+        <v>130741310</v>
       </c>
       <c r="B57" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7177,23 +7177,19 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
@@ -7201,10 +7197,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>444000</v>
+        <v>443891</v>
       </c>
       <c r="R57" t="n">
-        <v>7053028</v>
+        <v>7053029</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7237,11 +7233,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7268,10 +7259,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130741298</v>
+        <v>130741309</v>
       </c>
       <c r="B58" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7279,23 +7270,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7303,10 +7290,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443946</v>
+        <v>443836</v>
       </c>
       <c r="R58" t="n">
-        <v>7052921</v>
+        <v>7052967</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7339,11 +7326,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7370,10 +7352,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130741310</v>
+        <v>130734171</v>
       </c>
       <c r="B59" t="n">
-        <v>91781</v>
+        <v>79211</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7381,30 +7363,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443891</v>
+        <v>443981</v>
       </c>
       <c r="R59" t="n">
-        <v>7053029</v>
+        <v>7053488</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7439,34 +7428,65 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130741309</v>
+        <v>130741287</v>
       </c>
       <c r="B60" t="n">
-        <v>91781</v>
+        <v>57854</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7474,19 +7494,23 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7494,10 +7518,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443836</v>
+        <v>444000</v>
       </c>
       <c r="R60" t="n">
-        <v>7052967</v>
+        <v>7053028</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7530,6 +7554,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7556,10 +7585,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130734171</v>
+        <v>130741298</v>
       </c>
       <c r="B61" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7567,37 +7596,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443981</v>
+        <v>443946</v>
       </c>
       <c r="R61" t="n">
-        <v>7053488</v>
+        <v>7052921</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7634,7 +7660,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7643,44 +7669,18 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
-      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7822,10 +7822,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130741283</v>
+        <v>130741308</v>
       </c>
       <c r="B63" t="n">
-        <v>57854</v>
+        <v>91781</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7833,23 +7833,19 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
@@ -7857,10 +7853,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443927</v>
+        <v>444020</v>
       </c>
       <c r="R63" t="n">
-        <v>7052967</v>
+        <v>7053458</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7893,11 +7889,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7924,10 +7915,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130741308</v>
+        <v>130734172</v>
       </c>
       <c r="B64" t="n">
-        <v>91781</v>
+        <v>79211</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7935,30 +7926,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444020</v>
+        <v>444002</v>
       </c>
       <c r="R64" t="n">
-        <v>7053458</v>
+        <v>7053503</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7999,25 +7997,51 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130734172</v>
+        <v>130734179</v>
       </c>
       <c r="B65" t="n">
         <v>79211</v>
@@ -8055,10 +8079,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444002</v>
+        <v>443901</v>
       </c>
       <c r="R65" t="n">
-        <v>7053503</v>
+        <v>7053212</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8143,10 +8167,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130734179</v>
+        <v>130741283</v>
       </c>
       <c r="B66" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8154,37 +8178,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443901</v>
+        <v>443927</v>
       </c>
       <c r="R66" t="n">
-        <v>7053212</v>
+        <v>7052967</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8219,60 +8240,39 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130741280</v>
+        <v>130734184</v>
       </c>
       <c r="B67" t="n">
-        <v>57854</v>
+        <v>79211</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8280,34 +8280,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444040</v>
+        <v>444032</v>
       </c>
       <c r="R67" t="n">
-        <v>7053449</v>
+        <v>7053290</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8344,7 +8347,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Garnlav på en tydligt gammal gran i gles senvuxen granskog.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8353,28 +8356,54 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130734151</v>
+        <v>130734188</v>
       </c>
       <c r="B68" t="n">
-        <v>80317</v>
+        <v>79211</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8382,21 +8411,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -8409,10 +8438,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444218</v>
+        <v>444304</v>
       </c>
       <c r="R68" t="n">
-        <v>7053557</v>
+        <v>7053564</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8449,7 +8478,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Växer på en levande skadad sälg.</t>
+          <t>Växer på en tydligt gammal gran i relativt senvuxen gles granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8467,29 +8496,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med inslag av björk och enstaka sälg.</t>
-        </is>
-      </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8507,7 +8531,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130734184</v>
+        <v>130734191</v>
       </c>
       <c r="B69" t="n">
         <v>79211</v>
@@ -8545,10 +8569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444032</v>
+        <v>444407</v>
       </c>
       <c r="R69" t="n">
-        <v>7053290</v>
+        <v>7053726</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8585,7 +8609,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Garnlav på en tydligt gammal gran i gles senvuxen granskog.</t>
+          <t>Relativt rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8601,6 +8625,11 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -8638,7 +8667,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130734188</v>
+        <v>130734168</v>
       </c>
       <c r="B70" t="n">
         <v>79211</v>
@@ -8676,10 +8705,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444304</v>
+        <v>444293</v>
       </c>
       <c r="R70" t="n">
-        <v>7053564</v>
+        <v>7054016</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8712,11 +8741,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Växer på en tydligt gammal gran i relativt senvuxen gles granskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8769,7 +8793,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130734191</v>
+        <v>130734169</v>
       </c>
       <c r="B71" t="n">
         <v>79211</v>
@@ -8807,10 +8831,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444407</v>
+        <v>444160</v>
       </c>
       <c r="R71" t="n">
-        <v>7053726</v>
+        <v>7053858</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8847,7 +8871,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8863,11 +8887,6 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -8905,7 +8924,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130734168</v>
+        <v>130734183</v>
       </c>
       <c r="B72" t="n">
         <v>79211</v>
@@ -8943,10 +8962,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444293</v>
+        <v>443986</v>
       </c>
       <c r="R72" t="n">
-        <v>7054016</v>
+        <v>7053263</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8981,6 +9000,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran i gles senvuxen granskog.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8994,6 +9018,11 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med björk och inslag av asp.</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -9031,10 +9060,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130734169</v>
+        <v>130734151</v>
       </c>
       <c r="B73" t="n">
-        <v>79211</v>
+        <v>80317</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9042,21 +9071,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9069,10 +9098,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444160</v>
+        <v>444218</v>
       </c>
       <c r="R73" t="n">
-        <v>7053858</v>
+        <v>7053557</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9109,7 +9138,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Växer på en levande skadad sälg.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9127,24 +9156,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av björk och enstaka sälg.</t>
+        </is>
+      </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9162,10 +9196,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130734183</v>
+        <v>130741280</v>
       </c>
       <c r="B74" t="n">
-        <v>79211</v>
+        <v>57854</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9173,37 +9207,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>443986</v>
+        <v>444040</v>
       </c>
       <c r="R74" t="n">
-        <v>7053263</v>
+        <v>7053449</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9240,7 +9271,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På gran i gles senvuxen granskog.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9249,49 +9280,18 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med björk och inslag av asp.</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 61382-2025 artfynd.xlsx
+++ b/artfynd/A 61382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130734182</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130734186</v>
+        <v>130741286</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,37 +817,50 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444272</v>
+        <v>443968</v>
       </c>
       <c r="R3" t="n">
-        <v>7053547</v>
+        <v>7052990</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +897,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar i senvuxen äldre granskog.</t>
+          <t>Avbarkade en något klen gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,54 +906,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130741286</v>
+        <v>130734186</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>79219</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,50 +935,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443968</v>
+        <v>444272</v>
       </c>
       <c r="R4" t="n">
-        <v>7052990</v>
+        <v>7053547</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,7 +1002,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Avbarkade en något klen gran</t>
+          <t>Rikligt med garnlav på flera granar i senvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,18 +1011,44 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1058,7 +1058,7 @@
         <v>130734153</v>
       </c>
       <c r="B5" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         <v>130734193</v>
       </c>
       <c r="B6" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130741319</v>
+        <v>130734175</v>
       </c>
       <c r="B7" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,16 +1355,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444417</v>
+        <v>444124</v>
       </c>
       <c r="R7" t="n">
-        <v>7053741</v>
+        <v>7053447</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1401,7 +1404,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,28 +1413,54 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130734175</v>
+        <v>130741319</v>
       </c>
       <c r="B8" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,19 +1486,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444124</v>
+        <v>444417</v>
       </c>
       <c r="R8" t="n">
-        <v>7053447</v>
+        <v>7053741</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1506,7 +1532,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,54 +1541,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130734156</v>
+        <v>130741302</v>
       </c>
       <c r="B9" t="n">
-        <v>91781</v>
+        <v>57862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,37 +1570,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443886</v>
+        <v>443997</v>
       </c>
       <c r="R9" t="n">
-        <v>7053279</v>
+        <v>7053008</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1637,7 +1634,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en granhögstubbe.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,54 +1643,28 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130741302</v>
+        <v>130741291</v>
       </c>
       <c r="B10" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1725,10 +1696,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443997</v>
+        <v>443794</v>
       </c>
       <c r="R10" t="n">
-        <v>7053008</v>
+        <v>7053002</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1765,7 +1736,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1792,10 +1763,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130741291</v>
+        <v>130734145</v>
       </c>
       <c r="B11" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1821,16 +1792,24 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443794</v>
+        <v>443967</v>
       </c>
       <c r="R11" t="n">
-        <v>7053002</v>
+        <v>7053469</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,7 +1846,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1878,26 +1857,56 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog.</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130734145</v>
+        <v>130734156</v>
       </c>
       <c r="B12" t="n">
-        <v>57854</v>
+        <v>91794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,29 +1914,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1937,10 +1941,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443967</v>
+        <v>443886</v>
       </c>
       <c r="R12" t="n">
-        <v>7053469</v>
+        <v>7053279</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,7 +1981,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Gott om fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1986,6 +1990,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1994,11 +1999,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog.</t>
-        </is>
-      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130741320</v>
+        <v>130734164</v>
       </c>
       <c r="B13" t="n">
-        <v>89155</v>
+        <v>79219</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,34 +2045,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444326</v>
+        <v>444362</v>
       </c>
       <c r="R13" t="n">
-        <v>7053588</v>
+        <v>7054079</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,34 +2110,65 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>På gamla granar.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130734180</v>
+        <v>130741279</v>
       </c>
       <c r="B14" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,37 +2176,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443846</v>
+        <v>444007</v>
       </c>
       <c r="R14" t="n">
-        <v>7053252</v>
+        <v>7053457</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2209,7 +2240,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växer på grenar av en stående död gran med full längd (bhd ca 30 cm).</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2218,54 +2249,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130734170</v>
+        <v>130741320</v>
       </c>
       <c r="B15" t="n">
-        <v>79211</v>
+        <v>89167</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2273,37 +2278,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444133</v>
+        <v>444326</v>
       </c>
       <c r="R15" t="n">
-        <v>7053693</v>
+        <v>7053588</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2344,54 +2346,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130734164</v>
+        <v>130734180</v>
       </c>
       <c r="B16" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2426,10 +2402,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444362</v>
+        <v>443846</v>
       </c>
       <c r="R16" t="n">
-        <v>7054079</v>
+        <v>7053252</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2466,7 +2442,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På gamla granar.</t>
+          <t>Växer på grenar av en stående död gran med full längd (bhd ca 30 cm).</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2496,12 +2472,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2519,10 +2495,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130741279</v>
+        <v>130734170</v>
       </c>
       <c r="B17" t="n">
-        <v>57854</v>
+        <v>79219</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,34 +2506,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444007</v>
+        <v>444133</v>
       </c>
       <c r="R17" t="n">
-        <v>7053457</v>
+        <v>7053693</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2592,29 +2571,50 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2624,7 +2624,7 @@
         <v>130741317</v>
       </c>
       <c r="B18" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>130734190</v>
       </c>
       <c r="B19" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>130734177</v>
       </c>
       <c r="B20" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>130734192</v>
       </c>
       <c r="B21" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>130741284</v>
       </c>
       <c r="B22" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130734150</v>
+        <v>130741314</v>
       </c>
       <c r="B23" t="n">
-        <v>80317</v>
+        <v>91794</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,41 +3239,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444358</v>
+        <v>444416</v>
       </c>
       <c r="R23" t="n">
-        <v>7054049</v>
+        <v>7053728</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3308,70 +3297,34 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gott om bålar av skrovellav på en hyfsat grov sälg.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med björk och inslag av sälg.</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130734162</v>
+        <v>130734150</v>
       </c>
       <c r="B24" t="n">
-        <v>79211</v>
+        <v>80325</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3379,26 +3332,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3406,10 +3363,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444375</v>
+        <v>444358</v>
       </c>
       <c r="R24" t="n">
-        <v>7054118</v>
+        <v>7054049</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3444,6 +3401,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gott om bålar av skrovellav på en hyfsat grov sälg.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3459,24 +3421,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med björk och inslag av sälg.</t>
+        </is>
+      </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3494,10 +3461,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130741314</v>
+        <v>130734162</v>
       </c>
       <c r="B25" t="n">
-        <v>91781</v>
+        <v>79219</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3505,30 +3472,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444416</v>
+        <v>444375</v>
       </c>
       <c r="R25" t="n">
-        <v>7053728</v>
+        <v>7054118</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3569,18 +3543,44 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3590,7 +3590,7 @@
         <v>130734165</v>
       </c>
       <c r="B26" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>130734185</v>
       </c>
       <c r="B27" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>130741297</v>
       </c>
       <c r="B28" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>130741282</v>
       </c>
       <c r="B29" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>130741285</v>
       </c>
       <c r="B30" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4158,7 +4158,7 @@
         <v>130734181</v>
       </c>
       <c r="B31" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4286,10 +4286,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130734178</v>
+        <v>130741313</v>
       </c>
       <c r="B32" t="n">
-        <v>79211</v>
+        <v>91794</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4297,37 +4297,30 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443988</v>
+        <v>443985</v>
       </c>
       <c r="R32" t="n">
-        <v>7053189</v>
+        <v>7052983</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4362,65 +4355,34 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>På gammal gran i luckig äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130741313</v>
+        <v>130734178</v>
       </c>
       <c r="B33" t="n">
-        <v>91781</v>
+        <v>79219</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4428,30 +4390,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443985</v>
+        <v>443988</v>
       </c>
       <c r="R33" t="n">
-        <v>7052983</v>
+        <v>7053189</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4486,24 +4455,55 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gammal gran i luckig äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4513,7 +4513,7 @@
         <v>130741290</v>
       </c>
       <c r="B34" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>130734189</v>
       </c>
       <c r="B35" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,10 +4756,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130734176</v>
+        <v>130734174</v>
       </c>
       <c r="B36" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4794,10 +4794,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444149</v>
+        <v>444078</v>
       </c>
       <c r="R36" t="n">
-        <v>7053319</v>
+        <v>7053449</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På gran i gles äldre granskog.</t>
+          <t>Goda mängder garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4887,10 +4887,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130734174</v>
+        <v>130734176</v>
       </c>
       <c r="B37" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444078</v>
+        <v>444149</v>
       </c>
       <c r="R37" t="n">
-        <v>7053449</v>
+        <v>7053319</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4965,7 +4965,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Goda mängder garnlav på flera granar.</t>
+          <t>På gran i gles äldre granskog.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5021,7 +5021,7 @@
         <v>130741289</v>
       </c>
       <c r="B38" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>130741294</v>
       </c>
       <c r="B39" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5222,10 +5222,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130741318</v>
+        <v>130741292</v>
       </c>
       <c r="B40" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5233,21 +5233,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444153</v>
+        <v>443750</v>
       </c>
       <c r="R40" t="n">
-        <v>7053487</v>
+        <v>7052993</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5293,6 +5293,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5319,10 +5324,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130734173</v>
+        <v>130741301</v>
       </c>
       <c r="B41" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5330,37 +5335,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444046</v>
+        <v>443990</v>
       </c>
       <c r="R41" t="n">
-        <v>7053496</v>
+        <v>7052974</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5397,7 +5399,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På grenar av en stående död gran med full längd och 36 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5406,54 +5408,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130741292</v>
+        <v>130741295</v>
       </c>
       <c r="B42" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5485,10 +5461,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443750</v>
+        <v>443845</v>
       </c>
       <c r="R42" t="n">
-        <v>7052993</v>
+        <v>7052918</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5525,7 +5501,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5552,10 +5528,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130741301</v>
+        <v>130734144</v>
       </c>
       <c r="B43" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5581,16 +5557,24 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443990</v>
+        <v>444016</v>
       </c>
       <c r="R43" t="n">
-        <v>7052974</v>
+        <v>7053579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5627,7 +5611,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5638,26 +5622,51 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130741295</v>
+        <v>130741318</v>
       </c>
       <c r="B44" t="n">
-        <v>57854</v>
+        <v>79219</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5665,21 +5674,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5689,10 +5698,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443845</v>
+        <v>444153</v>
       </c>
       <c r="R44" t="n">
-        <v>7052918</v>
+        <v>7053487</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5725,11 +5734,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5756,10 +5760,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130734144</v>
+        <v>130734173</v>
       </c>
       <c r="B45" t="n">
-        <v>57854</v>
+        <v>79219</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5767,31 +5771,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5799,10 +5798,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444016</v>
+        <v>444046</v>
       </c>
       <c r="R45" t="n">
-        <v>7053579</v>
+        <v>7053496</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5839,7 +5838,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på stambasen av en gran.</t>
+          <t>På grenar av en stående död gran med full längd och 36 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5848,6 +5847,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
         <v>130734147</v>
       </c>
       <c r="B46" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>130741281</v>
       </c>
       <c r="B47" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>130734157</v>
       </c>
       <c r="B48" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>130741288</v>
       </c>
       <c r="B49" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>130741299</v>
       </c>
       <c r="B50" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>130734148</v>
       </c>
       <c r="B51" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>130734146</v>
       </c>
       <c r="B52" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>130734167</v>
       </c>
       <c r="B53" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>130741311</v>
       </c>
       <c r="B54" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>130741316</v>
       </c>
       <c r="B55" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>130741293</v>
       </c>
       <c r="B56" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130741310</v>
+        <v>130734171</v>
       </c>
       <c r="B57" t="n">
-        <v>91781</v>
+        <v>79219</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7177,30 +7177,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443891</v>
+        <v>443981</v>
       </c>
       <c r="R57" t="n">
-        <v>7053029</v>
+        <v>7053488</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7235,34 +7242,65 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130741309</v>
+        <v>130741287</v>
       </c>
       <c r="B58" t="n">
-        <v>91781</v>
+        <v>57862</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7270,19 +7308,23 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7290,10 +7332,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443836</v>
+        <v>444000</v>
       </c>
       <c r="R58" t="n">
-        <v>7052967</v>
+        <v>7053028</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7326,6 +7368,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7352,10 +7399,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130734171</v>
+        <v>130741298</v>
       </c>
       <c r="B59" t="n">
-        <v>79211</v>
+        <v>57862</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7363,37 +7410,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443981</v>
+        <v>443946</v>
       </c>
       <c r="R59" t="n">
-        <v>7053488</v>
+        <v>7052921</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7430,7 +7474,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7439,54 +7483,28 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130741287</v>
+        <v>130741310</v>
       </c>
       <c r="B60" t="n">
-        <v>57854</v>
+        <v>91794</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7494,23 +7512,19 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7518,10 +7532,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>444000</v>
+        <v>443891</v>
       </c>
       <c r="R60" t="n">
-        <v>7053028</v>
+        <v>7053029</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7554,11 +7568,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7585,10 +7594,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130741298</v>
+        <v>130741309</v>
       </c>
       <c r="B61" t="n">
-        <v>57854</v>
+        <v>91794</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7596,23 +7605,19 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7620,10 +7625,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443946</v>
+        <v>443836</v>
       </c>
       <c r="R61" t="n">
-        <v>7052921</v>
+        <v>7052967</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7656,11 +7661,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7690,7 +7690,7 @@
         <v>130734155</v>
       </c>
       <c r="B62" t="n">
-        <v>91757</v>
+        <v>91770</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>130741308</v>
       </c>
       <c r="B63" t="n">
-        <v>91781</v>
+        <v>91794</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7915,10 +7915,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130734172</v>
+        <v>130734179</v>
       </c>
       <c r="B64" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7953,10 +7953,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444002</v>
+        <v>443901</v>
       </c>
       <c r="R64" t="n">
-        <v>7053503</v>
+        <v>7053212</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8041,10 +8041,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130734179</v>
+        <v>130734172</v>
       </c>
       <c r="B65" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443901</v>
+        <v>444002</v>
       </c>
       <c r="R65" t="n">
-        <v>7053212</v>
+        <v>7053503</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8170,7 +8170,7 @@
         <v>130741283</v>
       </c>
       <c r="B66" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8272,7 +8272,7 @@
         <v>130734184</v>
       </c>
       <c r="B67" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>130734188</v>
       </c>
       <c r="B68" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8531,10 +8531,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130734191</v>
+        <v>130734169</v>
       </c>
       <c r="B69" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444407</v>
+        <v>444160</v>
       </c>
       <c r="R69" t="n">
-        <v>7053726</v>
+        <v>7053858</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8625,11 +8625,6 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -8667,10 +8662,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130734168</v>
+        <v>130734183</v>
       </c>
       <c r="B70" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8705,10 +8700,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444293</v>
+        <v>443986</v>
       </c>
       <c r="R70" t="n">
-        <v>7054016</v>
+        <v>7053263</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8743,6 +8738,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>På gran i gles senvuxen granskog.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8756,6 +8756,11 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med björk och inslag av asp.</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -8793,10 +8798,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130734169</v>
+        <v>130734191</v>
       </c>
       <c r="B71" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8831,10 +8836,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444160</v>
+        <v>444407</v>
       </c>
       <c r="R71" t="n">
-        <v>7053858</v>
+        <v>7053726</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8871,7 +8876,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Relativt rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8887,6 +8892,11 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -8924,10 +8934,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130734183</v>
+        <v>130734168</v>
       </c>
       <c r="B72" t="n">
-        <v>79211</v>
+        <v>79219</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8962,10 +8972,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443986</v>
+        <v>444293</v>
       </c>
       <c r="R72" t="n">
-        <v>7053263</v>
+        <v>7054016</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9000,11 +9010,6 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>På gran i gles senvuxen granskog.</t>
-        </is>
-      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9018,11 +9023,6 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med björk och inslag av asp.</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -9063,7 +9063,7 @@
         <v>130734151</v>
       </c>
       <c r="B73" t="n">
-        <v>80317</v>
+        <v>80325</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9199,7 +9199,7 @@
         <v>130741280</v>
       </c>
       <c r="B74" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>

--- a/artfynd/A 61382-2025 artfynd.xlsx
+++ b/artfynd/A 61382-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130734182</v>
       </c>
       <c r="B2" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130741286</v>
+        <v>130734186</v>
       </c>
       <c r="B3" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,50 +817,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443968</v>
+        <v>444272</v>
       </c>
       <c r="R3" t="n">
-        <v>7052990</v>
+        <v>7053547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -897,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Avbarkade en något klen gran</t>
+          <t>Rikligt med garnlav på flera granar i senvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,28 +893,54 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130734186</v>
+        <v>130741286</v>
       </c>
       <c r="B4" t="n">
-        <v>79219</v>
+        <v>57863</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,37 +948,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444272</v>
+        <v>443968</v>
       </c>
       <c r="R4" t="n">
-        <v>7053547</v>
+        <v>7052990</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1028,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar i senvuxen äldre granskog.</t>
+          <t>Avbarkade en något klen gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,54 +1037,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130734153</v>
+        <v>130734193</v>
       </c>
       <c r="B5" t="n">
-        <v>91770</v>
+        <v>79220</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,30 +1066,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1097,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443857</v>
+        <v>444436</v>
       </c>
       <c r="R5" t="n">
-        <v>7053224</v>
+        <v>7053798</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,11 +1131,6 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i stambasen av en stående grov gran med 50 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1157,7 +1148,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Flerskiktad äldre granskog med inslag av björk och enstaka asp.</t>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1172,12 +1163,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,10 +1186,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130734193</v>
+        <v>130734153</v>
       </c>
       <c r="B6" t="n">
-        <v>79219</v>
+        <v>91771</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,26 +1197,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1233,10 +1228,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444436</v>
+        <v>443857</v>
       </c>
       <c r="R6" t="n">
-        <v>7053798</v>
+        <v>7053224</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1271,6 +1266,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i stambasen av en stående grov gran med 50 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
+          <t>Flerskiktad äldre granskog med inslag av björk och enstaka asp.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130734175</v>
+        <v>130741319</v>
       </c>
       <c r="B7" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,19 +1355,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444124</v>
+        <v>444417</v>
       </c>
       <c r="R7" t="n">
-        <v>7053447</v>
+        <v>7053741</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1401,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,54 +1410,28 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130741319</v>
+        <v>130734175</v>
       </c>
       <c r="B8" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,16 +1457,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444417</v>
+        <v>444124</v>
       </c>
       <c r="R8" t="n">
-        <v>7053741</v>
+        <v>7053447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1532,7 +1506,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,28 +1515,54 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130741302</v>
+        <v>130734156</v>
       </c>
       <c r="B9" t="n">
-        <v>57862</v>
+        <v>91795</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,34 +1570,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443997</v>
+        <v>443886</v>
       </c>
       <c r="R9" t="n">
-        <v>7053008</v>
+        <v>7053279</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,7 +1637,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Gott om fruktkroppar i en granhögstubbe.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,28 +1646,54 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130741291</v>
+        <v>130741302</v>
       </c>
       <c r="B10" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,10 +1725,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443794</v>
+        <v>443997</v>
       </c>
       <c r="R10" t="n">
-        <v>7053002</v>
+        <v>7053008</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1736,7 +1765,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1763,10 +1792,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130734145</v>
+        <v>130741291</v>
       </c>
       <c r="B11" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1792,24 +1821,16 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443967</v>
+        <v>443794</v>
       </c>
       <c r="R11" t="n">
-        <v>7053469</v>
+        <v>7053002</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1846,7 +1867,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,56 +1878,26 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog.</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130734156</v>
+        <v>130734145</v>
       </c>
       <c r="B12" t="n">
-        <v>91794</v>
+        <v>57863</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1914,24 +1905,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1941,10 +1937,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443886</v>
+        <v>443967</v>
       </c>
       <c r="R12" t="n">
-        <v>7053279</v>
+        <v>7053469</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1981,7 +1977,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i en granhögstubbe.</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1990,7 +1986,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1999,6 +1994,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog.</t>
+        </is>
+      </c>
       <c r="AJ12" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2034,10 +2034,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130734164</v>
+        <v>130741320</v>
       </c>
       <c r="B13" t="n">
-        <v>79219</v>
+        <v>89168</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2045,37 +2045,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444362</v>
+        <v>444326</v>
       </c>
       <c r="R13" t="n">
-        <v>7054079</v>
+        <v>7053588</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2110,65 +2107,34 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På gamla granar.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130741279</v>
+        <v>130734180</v>
       </c>
       <c r="B14" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2176,34 +2142,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444007</v>
+        <v>443846</v>
       </c>
       <c r="R14" t="n">
-        <v>7053457</v>
+        <v>7053252</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2240,7 +2209,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Växer på grenar av en stående död gran med full längd (bhd ca 30 cm).</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2249,28 +2218,54 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130741320</v>
+        <v>130734170</v>
       </c>
       <c r="B15" t="n">
-        <v>89167</v>
+        <v>79220</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2278,34 +2273,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444326</v>
+        <v>444133</v>
       </c>
       <c r="R15" t="n">
-        <v>7053588</v>
+        <v>7053693</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2346,28 +2344,54 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130734180</v>
+        <v>130734164</v>
       </c>
       <c r="B16" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2402,10 +2426,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>443846</v>
+        <v>444362</v>
       </c>
       <c r="R16" t="n">
-        <v>7053252</v>
+        <v>7054079</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2442,7 +2466,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Växer på grenar av en stående död gran med full längd (bhd ca 30 cm).</t>
+          <t>På gamla granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2472,12 +2496,12 @@
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2495,10 +2519,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130734170</v>
+        <v>130741279</v>
       </c>
       <c r="B17" t="n">
-        <v>79219</v>
+        <v>57863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2506,37 +2530,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444133</v>
+        <v>444007</v>
       </c>
       <c r="R17" t="n">
-        <v>7053693</v>
+        <v>7053457</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2571,50 +2592,29 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2624,7 +2624,7 @@
         <v>130741317</v>
       </c>
       <c r="B18" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>130734190</v>
       </c>
       <c r="B19" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>130734177</v>
       </c>
       <c r="B20" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>130734192</v>
       </c>
       <c r="B21" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>130741284</v>
       </c>
       <c r="B22" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
         <v>130741314</v>
       </c>
       <c r="B23" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>130734150</v>
       </c>
       <c r="B24" t="n">
-        <v>80325</v>
+        <v>80326</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>130734162</v>
       </c>
       <c r="B25" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>130734165</v>
       </c>
       <c r="B26" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3721,7 +3721,7 @@
         <v>130734185</v>
       </c>
       <c r="B27" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3852,7 +3852,7 @@
         <v>130741297</v>
       </c>
       <c r="B28" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3954,7 +3954,7 @@
         <v>130741282</v>
       </c>
       <c r="B29" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4056,7 +4056,7 @@
         <v>130741285</v>
       </c>
       <c r="B30" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4155,10 +4155,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130734181</v>
+        <v>130741313</v>
       </c>
       <c r="B31" t="n">
-        <v>79219</v>
+        <v>91795</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4166,37 +4166,30 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443859</v>
+        <v>443985</v>
       </c>
       <c r="R31" t="n">
-        <v>7053310</v>
+        <v>7052983</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4231,65 +4224,34 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På gammal gran.</t>
-        </is>
-      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130741313</v>
+        <v>130734181</v>
       </c>
       <c r="B32" t="n">
-        <v>91794</v>
+        <v>79220</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4297,30 +4259,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443985</v>
+        <v>443859</v>
       </c>
       <c r="R32" t="n">
-        <v>7052983</v>
+        <v>7053310</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4355,24 +4324,55 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>På gammal gran.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4382,7 +4382,7 @@
         <v>130734178</v>
       </c>
       <c r="B33" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>130741290</v>
       </c>
       <c r="B34" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4620,10 +4620,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130734189</v>
+        <v>130734174</v>
       </c>
       <c r="B35" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4658,10 +4658,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444342</v>
+        <v>444078</v>
       </c>
       <c r="R35" t="n">
-        <v>7053646</v>
+        <v>7053449</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlavsbålar på gran.</t>
+          <t>Goda mängder garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4714,11 +4714,6 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI35" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -4756,10 +4751,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130734174</v>
+        <v>130734189</v>
       </c>
       <c r="B36" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4794,10 +4789,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444078</v>
+        <v>444342</v>
       </c>
       <c r="R36" t="n">
-        <v>7053449</v>
+        <v>7053646</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4834,7 +4829,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Goda mängder garnlav på flera granar.</t>
+          <t>Relativt rikligt med garnlavsbålar på gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4850,6 +4845,11 @@
       <c r="AH36" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ36" t="inlineStr">
@@ -4890,7 +4890,7 @@
         <v>130734176</v>
       </c>
       <c r="B37" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>130741289</v>
       </c>
       <c r="B38" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>130741294</v>
       </c>
       <c r="B39" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5222,10 +5222,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130741292</v>
+        <v>130741318</v>
       </c>
       <c r="B40" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5233,21 +5233,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>443750</v>
+        <v>444153</v>
       </c>
       <c r="R40" t="n">
-        <v>7052993</v>
+        <v>7053487</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5293,11 +5293,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5324,10 +5319,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130741301</v>
+        <v>130734173</v>
       </c>
       <c r="B41" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5335,34 +5330,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443990</v>
+        <v>444046</v>
       </c>
       <c r="R41" t="n">
-        <v>7052974</v>
+        <v>7053496</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5399,7 +5397,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På grenar av en stående död gran med full längd och 36 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5408,28 +5406,54 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130741295</v>
+        <v>130741292</v>
       </c>
       <c r="B42" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5461,10 +5485,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443845</v>
+        <v>443750</v>
       </c>
       <c r="R42" t="n">
-        <v>7052918</v>
+        <v>7052993</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5501,7 +5525,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5528,10 +5552,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130734144</v>
+        <v>130741301</v>
       </c>
       <c r="B43" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5557,24 +5581,16 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>444016</v>
+        <v>443990</v>
       </c>
       <c r="R43" t="n">
-        <v>7053579</v>
+        <v>7052974</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5611,7 +5627,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5622,51 +5638,26 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130741318</v>
+        <v>130741295</v>
       </c>
       <c r="B44" t="n">
-        <v>79219</v>
+        <v>57863</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5674,21 +5665,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5698,10 +5689,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444153</v>
+        <v>443845</v>
       </c>
       <c r="R44" t="n">
-        <v>7053487</v>
+        <v>7052918</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5734,6 +5725,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5760,10 +5756,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130734173</v>
+        <v>130734144</v>
       </c>
       <c r="B45" t="n">
-        <v>79219</v>
+        <v>57863</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5771,26 +5767,31 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5798,10 +5799,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444046</v>
+        <v>444016</v>
       </c>
       <c r="R45" t="n">
-        <v>7053496</v>
+        <v>7053579</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5838,7 +5839,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>På grenar av en stående död gran med full längd och 36 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5847,7 +5848,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
         <v>130734147</v>
       </c>
       <c r="B46" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>130741281</v>
       </c>
       <c r="B47" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>130734157</v>
       </c>
       <c r="B48" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>130741288</v>
       </c>
       <c r="B49" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6369,7 +6369,7 @@
         <v>130741299</v>
       </c>
       <c r="B50" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6471,7 +6471,7 @@
         <v>130734148</v>
       </c>
       <c r="B51" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6606,7 +6606,7 @@
         <v>130734146</v>
       </c>
       <c r="B52" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>130734167</v>
       </c>
       <c r="B53" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6869,10 +6869,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130741311</v>
+        <v>130741316</v>
       </c>
       <c r="B54" t="n">
-        <v>91794</v>
+        <v>79220</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6880,19 +6880,23 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
@@ -6900,10 +6904,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443991</v>
+        <v>444000</v>
       </c>
       <c r="R54" t="n">
-        <v>7052955</v>
+        <v>7053558</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6936,6 +6940,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6962,10 +6971,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130741316</v>
+        <v>130741311</v>
       </c>
       <c r="B55" t="n">
-        <v>79219</v>
+        <v>91795</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6973,23 +6982,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6997,10 +7002,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444000</v>
+        <v>443991</v>
       </c>
       <c r="R55" t="n">
-        <v>7053558</v>
+        <v>7052955</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7033,11 +7038,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7067,7 +7067,7 @@
         <v>130741293</v>
       </c>
       <c r="B56" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7169,7 +7169,7 @@
         <v>130734171</v>
       </c>
       <c r="B57" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7300,7 +7300,7 @@
         <v>130741287</v>
       </c>
       <c r="B58" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>130741298</v>
       </c>
       <c r="B59" t="n">
-        <v>57862</v>
+        <v>57863</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7504,7 +7504,7 @@
         <v>130741310</v>
       </c>
       <c r="B60" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>130741309</v>
       </c>
       <c r="B61" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7687,10 +7687,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130734155</v>
+        <v>130741283</v>
       </c>
       <c r="B62" t="n">
-        <v>91770</v>
+        <v>57863</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7698,41 +7698,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443861</v>
+        <v>443927</v>
       </c>
       <c r="R62" t="n">
-        <v>7053306</v>
+        <v>7052967</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7769,7 +7762,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en levande relativt grov gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7778,44 +7771,18 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7825,7 +7792,7 @@
         <v>130741308</v>
       </c>
       <c r="B63" t="n">
-        <v>91794</v>
+        <v>91795</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7915,10 +7882,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130734179</v>
+        <v>130734155</v>
       </c>
       <c r="B64" t="n">
-        <v>79219</v>
+        <v>91771</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7926,26 +7893,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7953,10 +7924,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443901</v>
+        <v>443861</v>
       </c>
       <c r="R64" t="n">
-        <v>7053212</v>
+        <v>7053306</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7991,6 +7962,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i stambasen av en levande relativt grov gran.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8018,12 +7994,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8044,7 +8020,7 @@
         <v>130734172</v>
       </c>
       <c r="B65" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8167,10 +8143,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130741283</v>
+        <v>130734179</v>
       </c>
       <c r="B66" t="n">
-        <v>57862</v>
+        <v>79220</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8178,34 +8154,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443927</v>
+        <v>443901</v>
       </c>
       <c r="R66" t="n">
-        <v>7052967</v>
+        <v>7053212</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8240,29 +8219,50 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8272,7 +8272,7 @@
         <v>130734184</v>
       </c>
       <c r="B67" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>130734188</v>
       </c>
       <c r="B68" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8531,10 +8531,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130734169</v>
+        <v>130734191</v>
       </c>
       <c r="B69" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444160</v>
+        <v>444407</v>
       </c>
       <c r="R69" t="n">
-        <v>7053858</v>
+        <v>7053726</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Relativt rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8625,6 +8625,11 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI69" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -8662,10 +8667,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130734183</v>
+        <v>130734168</v>
       </c>
       <c r="B70" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8700,10 +8705,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>443986</v>
+        <v>444293</v>
       </c>
       <c r="R70" t="n">
-        <v>7053263</v>
+        <v>7054016</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8738,11 +8743,6 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>På gran i gles senvuxen granskog.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8756,11 +8756,6 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med björk och inslag av asp.</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -8798,10 +8793,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130734191</v>
+        <v>130734169</v>
       </c>
       <c r="B71" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8836,10 +8831,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444407</v>
+        <v>444160</v>
       </c>
       <c r="R71" t="n">
-        <v>7053726</v>
+        <v>7053858</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8876,7 +8871,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på gran.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8892,11 +8887,6 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -8934,10 +8924,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130734168</v>
+        <v>130734183</v>
       </c>
       <c r="B72" t="n">
-        <v>79219</v>
+        <v>79220</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8972,10 +8962,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444293</v>
+        <v>443986</v>
       </c>
       <c r="R72" t="n">
-        <v>7054016</v>
+        <v>7053263</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9010,6 +9000,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>På gran i gles senvuxen granskog.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9023,6 +9018,11 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med björk och inslag av asp.</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -9060,10 +9060,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130734151</v>
+        <v>130741280</v>
       </c>
       <c r="B73" t="n">
-        <v>80325</v>
+        <v>57863</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9071,37 +9071,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444218</v>
+        <v>444040</v>
       </c>
       <c r="R73" t="n">
-        <v>7053557</v>
+        <v>7053449</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9138,7 +9135,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Växer på en levande skadad sälg.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9147,59 +9144,28 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med inslag av björk och enstaka sälg.</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130741280</v>
+        <v>130734151</v>
       </c>
       <c r="B74" t="n">
-        <v>57862</v>
+        <v>80326</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,34 +9173,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444040</v>
+        <v>444218</v>
       </c>
       <c r="R74" t="n">
-        <v>7053449</v>
+        <v>7053557</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9271,7 +9240,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Växer på en levande skadad sälg.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9280,18 +9249,49 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av björk och enstaka sälg.</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 61382-2025 artfynd.xlsx
+++ b/artfynd/A 61382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130734182</v>
+        <v>130741286</v>
       </c>
       <c r="B2" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443903</v>
+        <v>443968</v>
       </c>
       <c r="R2" t="n">
-        <v>7053286</v>
+        <v>7052990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +766,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog.</t>
+          <t>Avbarkade en något klen gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,54 +775,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130734186</v>
+        <v>130734182</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444272</v>
+        <v>443903</v>
       </c>
       <c r="R3" t="n">
-        <v>7053547</v>
+        <v>7053286</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar i senvuxen äldre granskog.</t>
+          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130741286</v>
+        <v>130734186</v>
       </c>
       <c r="B4" t="n">
-        <v>57863</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,50 +935,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443968</v>
+        <v>444272</v>
       </c>
       <c r="R4" t="n">
-        <v>7052990</v>
+        <v>7053547</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,7 +1002,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Avbarkade en något klen gran</t>
+          <t>Rikligt med garnlav på flera granar i senvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,28 +1011,54 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130734193</v>
+        <v>130734153</v>
       </c>
       <c r="B5" t="n">
-        <v>79220</v>
+        <v>91772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,26 +1066,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1093,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444436</v>
+        <v>443857</v>
       </c>
       <c r="R5" t="n">
-        <v>7053798</v>
+        <v>7053224</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,6 +1135,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i stambasen av en stående grov gran med 50 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1148,7 +1157,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
+          <t>Flerskiktad äldre granskog med inslag av björk och enstaka asp.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1163,12 +1172,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1186,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130734153</v>
+        <v>130734193</v>
       </c>
       <c r="B6" t="n">
-        <v>91771</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,30 +1206,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1228,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443857</v>
+        <v>444436</v>
       </c>
       <c r="R6" t="n">
-        <v>7053224</v>
+        <v>7053798</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,11 +1271,6 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i stambasen av en stående grov gran med 50 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Flerskiktad äldre granskog med inslag av björk och enstaka asp.</t>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1326,10 +1326,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130741319</v>
+        <v>130734175</v>
       </c>
       <c r="B7" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,16 +1355,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444417</v>
+        <v>444124</v>
       </c>
       <c r="R7" t="n">
-        <v>7053741</v>
+        <v>7053447</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1401,7 +1404,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,28 +1413,54 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130734175</v>
+        <v>130741319</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1457,19 +1486,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444124</v>
+        <v>444417</v>
       </c>
       <c r="R8" t="n">
-        <v>7053447</v>
+        <v>7053741</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1506,7 +1532,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1515,44 +1541,18 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1562,7 +1562,7 @@
         <v>130734156</v>
       </c>
       <c r="B9" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1690,10 +1690,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130741302</v>
+        <v>130734145</v>
       </c>
       <c r="B10" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1719,16 +1719,24 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443997</v>
+        <v>443967</v>
       </c>
       <c r="R10" t="n">
-        <v>7053008</v>
+        <v>7053469</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1765,7 +1773,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1776,26 +1784,56 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog.</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130741291</v>
+        <v>130741302</v>
       </c>
       <c r="B11" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1827,10 +1865,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443794</v>
+        <v>443997</v>
       </c>
       <c r="R11" t="n">
-        <v>7053002</v>
+        <v>7053008</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1867,7 +1905,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1894,10 +1932,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130734145</v>
+        <v>130741291</v>
       </c>
       <c r="B12" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,24 +1961,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443967</v>
+        <v>443794</v>
       </c>
       <c r="R12" t="n">
-        <v>7053469</v>
+        <v>7053002</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1977,7 +2007,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1988,46 +2018,16 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog.</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2037,7 +2037,7 @@
         <v>130741320</v>
       </c>
       <c r="B13" t="n">
-        <v>89168</v>
+        <v>89169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>130734180</v>
       </c>
       <c r="B14" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         <v>130734170</v>
       </c>
       <c r="B15" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         <v>130734164</v>
       </c>
       <c r="B16" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>130741279</v>
       </c>
       <c r="B17" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>130741317</v>
       </c>
       <c r="B18" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>130734190</v>
       </c>
       <c r="B19" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>130734177</v>
       </c>
       <c r="B20" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2993,7 +2993,7 @@
         <v>130734192</v>
       </c>
       <c r="B21" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3129,7 +3129,7 @@
         <v>130741284</v>
       </c>
       <c r="B22" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130741314</v>
+        <v>130734150</v>
       </c>
       <c r="B23" t="n">
-        <v>91795</v>
+        <v>80327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,30 +3239,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444416</v>
+        <v>444358</v>
       </c>
       <c r="R23" t="n">
-        <v>7053728</v>
+        <v>7054049</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3297,34 +3308,70 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gott om bålar av skrovellav på en hyfsat grov sälg.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med björk och inslag av sälg.</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130734150</v>
+        <v>130741314</v>
       </c>
       <c r="B24" t="n">
-        <v>80326</v>
+        <v>91796</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3332,41 +3379,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444358</v>
+        <v>444416</v>
       </c>
       <c r="R24" t="n">
-        <v>7054049</v>
+        <v>7053728</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3401,60 +3437,24 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gott om bålar av skrovellav på en hyfsat grov sälg.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med björk och inslag av sälg.</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3464,7 +3464,7 @@
         <v>130734162</v>
       </c>
       <c r="B25" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3587,10 +3587,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130734165</v>
+        <v>130734185</v>
       </c>
       <c r="B26" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444343</v>
+        <v>444157</v>
       </c>
       <c r="R26" t="n">
-        <v>7054057</v>
+        <v>7053507</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3718,10 +3718,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130734185</v>
+        <v>130734165</v>
       </c>
       <c r="B27" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444157</v>
+        <v>444343</v>
       </c>
       <c r="R27" t="n">
-        <v>7053507</v>
+        <v>7054057</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3849,10 +3849,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130741297</v>
+        <v>130741285</v>
       </c>
       <c r="B28" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443871</v>
+        <v>443963</v>
       </c>
       <c r="R28" t="n">
-        <v>7052942</v>
+        <v>7052972</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3954,7 +3954,7 @@
         <v>130741282</v>
       </c>
       <c r="B29" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4053,10 +4053,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130741285</v>
+        <v>130741297</v>
       </c>
       <c r="B30" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443963</v>
+        <v>443871</v>
       </c>
       <c r="R30" t="n">
-        <v>7052972</v>
+        <v>7052942</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4158,7 +4158,7 @@
         <v>130741313</v>
       </c>
       <c r="B31" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4251,7 +4251,7 @@
         <v>130734181</v>
       </c>
       <c r="B32" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4382,7 +4382,7 @@
         <v>130734178</v>
       </c>
       <c r="B33" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4513,7 +4513,7 @@
         <v>130741290</v>
       </c>
       <c r="B34" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4623,7 +4623,7 @@
         <v>130734174</v>
       </c>
       <c r="B35" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>130734189</v>
       </c>
       <c r="B36" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>130734176</v>
       </c>
       <c r="B37" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>130741289</v>
       </c>
       <c r="B38" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
         <v>130741294</v>
       </c>
       <c r="B39" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5222,10 +5222,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130741318</v>
+        <v>130734173</v>
       </c>
       <c r="B40" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5251,16 +5251,19 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444153</v>
+        <v>444046</v>
       </c>
       <c r="R40" t="n">
-        <v>7053487</v>
+        <v>7053496</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5295,34 +5298,65 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På grenar av en stående död gran med full längd och 36 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130734173</v>
+        <v>130741295</v>
       </c>
       <c r="B41" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5330,37 +5364,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444046</v>
+        <v>443845</v>
       </c>
       <c r="R41" t="n">
-        <v>7053496</v>
+        <v>7052918</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5397,7 +5428,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På grenar av en stående död gran med full längd och 36 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5406,54 +5437,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130741292</v>
+        <v>130741301</v>
       </c>
       <c r="B42" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5485,10 +5490,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443750</v>
+        <v>443990</v>
       </c>
       <c r="R42" t="n">
-        <v>7052993</v>
+        <v>7052974</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5525,7 +5530,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5552,10 +5557,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130741301</v>
+        <v>130741292</v>
       </c>
       <c r="B43" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5587,10 +5592,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443990</v>
+        <v>443750</v>
       </c>
       <c r="R43" t="n">
-        <v>7052974</v>
+        <v>7052993</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5627,7 +5632,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5654,10 +5659,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130741295</v>
+        <v>130734144</v>
       </c>
       <c r="B44" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5683,16 +5688,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443845</v>
+        <v>444016</v>
       </c>
       <c r="R44" t="n">
-        <v>7052918</v>
+        <v>7053579</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5729,7 +5742,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5740,26 +5753,51 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130734144</v>
+        <v>130741318</v>
       </c>
       <c r="B45" t="n">
-        <v>57863</v>
+        <v>79221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5767,42 +5805,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444016</v>
+        <v>444153</v>
       </c>
       <c r="R45" t="n">
-        <v>7053579</v>
+        <v>7053487</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5837,11 +5867,6 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack, färska, på stambasen av en gran.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5850,41 +5875,16 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
         <v>130734147</v>
       </c>
       <c r="B46" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6034,7 +6034,7 @@
         <v>130741281</v>
       </c>
       <c r="B47" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6136,7 +6136,7 @@
         <v>130734157</v>
       </c>
       <c r="B48" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6264,10 +6264,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130741288</v>
+        <v>130734146</v>
       </c>
       <c r="B49" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6293,16 +6293,24 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443996</v>
+        <v>443949</v>
       </c>
       <c r="R49" t="n">
-        <v>7053048</v>
+        <v>7053197</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6339,7 +6347,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska, enstaka på stambasen av en gammal gran.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6350,26 +6358,51 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130741299</v>
+        <v>130734148</v>
       </c>
       <c r="B50" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6395,16 +6428,24 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443972</v>
+        <v>444153</v>
       </c>
       <c r="R50" t="n">
-        <v>7052967</v>
+        <v>7053496</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6441,7 +6482,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, äldre och ev. något färskt, på stambasen av en gran. Medelhögt till högt livsmiljövärde på fyndplatsen baserat på volym stående död ved av gran.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6452,26 +6493,51 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130734148</v>
+        <v>130741288</v>
       </c>
       <c r="B51" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6497,24 +6563,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444153</v>
+        <v>443996</v>
       </c>
       <c r="R51" t="n">
-        <v>7053496</v>
+        <v>7053048</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6551,7 +6609,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och ev. något färskt, på stambasen av en gran. Medelhögt till högt livsmiljövärde på fyndplatsen baserat på volym stående död ved av gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6562,51 +6620,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130734146</v>
+        <v>130741299</v>
       </c>
       <c r="B52" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6632,24 +6665,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443949</v>
+        <v>443972</v>
       </c>
       <c r="R52" t="n">
-        <v>7053197</v>
+        <v>7052967</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6686,7 +6711,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på stambasen av en gammal gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6697,41 +6722,16 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6741,7 +6741,7 @@
         <v>130734167</v>
       </c>
       <c r="B53" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>130741316</v>
       </c>
       <c r="B54" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>130741311</v>
       </c>
       <c r="B55" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7067,7 +7067,7 @@
         <v>130741293</v>
       </c>
       <c r="B56" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7166,10 +7166,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130734171</v>
+        <v>130741309</v>
       </c>
       <c r="B57" t="n">
-        <v>79220</v>
+        <v>91796</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7177,37 +7177,30 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443981</v>
+        <v>443836</v>
       </c>
       <c r="R57" t="n">
-        <v>7053488</v>
+        <v>7052967</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7242,65 +7235,34 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130741287</v>
+        <v>130741310</v>
       </c>
       <c r="B58" t="n">
-        <v>57863</v>
+        <v>91796</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7308,23 +7270,19 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
@@ -7332,10 +7290,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>444000</v>
+        <v>443891</v>
       </c>
       <c r="R58" t="n">
-        <v>7053028</v>
+        <v>7053029</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7368,11 +7326,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7399,10 +7352,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130741298</v>
+        <v>130734171</v>
       </c>
       <c r="B59" t="n">
-        <v>57863</v>
+        <v>79221</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7410,34 +7363,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>443946</v>
+        <v>443981</v>
       </c>
       <c r="R59" t="n">
-        <v>7052921</v>
+        <v>7053488</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7474,7 +7430,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7483,28 +7439,54 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130741310</v>
+        <v>130741298</v>
       </c>
       <c r="B60" t="n">
-        <v>91795</v>
+        <v>57864</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7512,19 +7494,23 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
@@ -7532,10 +7518,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443891</v>
+        <v>443946</v>
       </c>
       <c r="R60" t="n">
-        <v>7053029</v>
+        <v>7052921</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7568,6 +7554,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7594,10 +7585,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130741309</v>
+        <v>130741287</v>
       </c>
       <c r="B61" t="n">
-        <v>91795</v>
+        <v>57864</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7605,19 +7596,23 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7625,10 +7620,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443836</v>
+        <v>444000</v>
       </c>
       <c r="R61" t="n">
-        <v>7052967</v>
+        <v>7053028</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7661,6 +7656,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7687,10 +7687,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130741283</v>
+        <v>130734155</v>
       </c>
       <c r="B62" t="n">
-        <v>57863</v>
+        <v>91772</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7698,34 +7698,41 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443927</v>
+        <v>443861</v>
       </c>
       <c r="R62" t="n">
-        <v>7052967</v>
+        <v>7053306</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7762,7 +7769,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Flera fruktkroppar i stambasen av en levande relativt grov gran.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7771,18 +7778,44 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
+      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7792,7 +7825,7 @@
         <v>130741308</v>
       </c>
       <c r="B63" t="n">
-        <v>91795</v>
+        <v>91796</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7882,10 +7915,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130734155</v>
+        <v>130734179</v>
       </c>
       <c r="B64" t="n">
-        <v>91771</v>
+        <v>79221</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7893,30 +7926,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -7924,10 +7953,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443861</v>
+        <v>443901</v>
       </c>
       <c r="R64" t="n">
-        <v>7053306</v>
+        <v>7053212</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7962,11 +7991,6 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i stambasen av en levande relativt grov gran.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7994,12 +8018,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8020,7 +8044,7 @@
         <v>130734172</v>
       </c>
       <c r="B65" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8143,10 +8167,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130734179</v>
+        <v>130741283</v>
       </c>
       <c r="B66" t="n">
-        <v>79220</v>
+        <v>57864</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8154,37 +8178,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443901</v>
+        <v>443927</v>
       </c>
       <c r="R66" t="n">
-        <v>7053212</v>
+        <v>7052967</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8219,50 +8240,29 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8272,7 +8272,7 @@
         <v>130734184</v>
       </c>
       <c r="B67" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>130734188</v>
       </c>
       <c r="B68" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>130734191</v>
       </c>
       <c r="B69" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8670,7 +8670,7 @@
         <v>130734168</v>
       </c>
       <c r="B70" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8796,7 +8796,7 @@
         <v>130734169</v>
       </c>
       <c r="B71" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>130734183</v>
       </c>
       <c r="B72" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9060,10 +9060,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130741280</v>
+        <v>130734151</v>
       </c>
       <c r="B73" t="n">
-        <v>57863</v>
+        <v>80327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9071,34 +9071,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444040</v>
+        <v>444218</v>
       </c>
       <c r="R73" t="n">
-        <v>7053449</v>
+        <v>7053557</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9135,7 +9138,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Växer på en levande skadad sälg.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9144,28 +9147,59 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av björk och enstaka sälg.</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130734151</v>
+        <v>130741280</v>
       </c>
       <c r="B74" t="n">
-        <v>80326</v>
+        <v>57864</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9173,37 +9207,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444218</v>
+        <v>444040</v>
       </c>
       <c r="R74" t="n">
-        <v>7053557</v>
+        <v>7053449</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9240,7 +9271,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Växer på en levande skadad sälg.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9249,49 +9280,18 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med inslag av björk och enstaka sälg.</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 61382-2025 artfynd.xlsx
+++ b/artfynd/A 61382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130741286</v>
+        <v>130734182</v>
       </c>
       <c r="B2" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,50 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443968</v>
+        <v>443903</v>
       </c>
       <c r="R2" t="n">
-        <v>7052990</v>
+        <v>7053286</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Avbarkade en något klen gran</t>
+          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,25 +762,51 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130734182</v>
+        <v>130734186</v>
       </c>
       <c r="B3" t="n">
         <v>79221</v>
@@ -831,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443903</v>
+        <v>444272</v>
       </c>
       <c r="R3" t="n">
-        <v>7053286</v>
+        <v>7053547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog.</t>
+          <t>Rikligt med garnlav på flera granar i senvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130734186</v>
+        <v>130741286</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,37 +948,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444272</v>
+        <v>443968</v>
       </c>
       <c r="R4" t="n">
-        <v>7053547</v>
+        <v>7052990</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1028,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar i senvuxen äldre granskog.</t>
+          <t>Avbarkade en något klen gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,54 +1037,28 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130734153</v>
+        <v>130734193</v>
       </c>
       <c r="B5" t="n">
-        <v>91772</v>
+        <v>79221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,30 +1066,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1097,10 +1093,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>443857</v>
+        <v>444436</v>
       </c>
       <c r="R5" t="n">
-        <v>7053224</v>
+        <v>7053798</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1135,11 +1131,6 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i stambasen av en stående grov gran med 50 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1157,7 +1148,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Flerskiktad äldre granskog med inslag av björk och enstaka asp.</t>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1172,12 +1163,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1195,10 +1186,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130734193</v>
+        <v>130734153</v>
       </c>
       <c r="B6" t="n">
-        <v>79221</v>
+        <v>91772</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1206,26 +1197,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1233,10 +1228,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>444436</v>
+        <v>443857</v>
       </c>
       <c r="R6" t="n">
-        <v>7053798</v>
+        <v>7053224</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1271,6 +1266,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i stambasen av en stående grov gran med 50 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
+          <t>Flerskiktad äldre granskog med inslag av björk och enstaka asp.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1326,7 +1326,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130734175</v>
+        <v>130741319</v>
       </c>
       <c r="B7" t="n">
         <v>79221</v>
@@ -1355,19 +1355,16 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444124</v>
+        <v>444417</v>
       </c>
       <c r="R7" t="n">
-        <v>7053447</v>
+        <v>7053741</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1401,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Långväxta bålar på gran.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1413,51 +1410,25 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130741319</v>
+        <v>130734175</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1486,16 +1457,19 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444417</v>
+        <v>444124</v>
       </c>
       <c r="R8" t="n">
-        <v>7053741</v>
+        <v>7053447</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1532,7 +1506,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1541,18 +1515,44 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -3587,7 +3587,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130734185</v>
+        <v>130734165</v>
       </c>
       <c r="B26" t="n">
         <v>79221</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444157</v>
+        <v>444343</v>
       </c>
       <c r="R26" t="n">
-        <v>7053507</v>
+        <v>7054057</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3718,7 +3718,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130734165</v>
+        <v>130734185</v>
       </c>
       <c r="B27" t="n">
         <v>79221</v>
@@ -3756,10 +3756,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444343</v>
+        <v>444157</v>
       </c>
       <c r="R27" t="n">
-        <v>7054057</v>
+        <v>7053507</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3796,7 +3796,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4155,10 +4155,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130741313</v>
+        <v>130741290</v>
       </c>
       <c r="B31" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4166,30 +4166,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443985</v>
+        <v>444005</v>
       </c>
       <c r="R31" t="n">
-        <v>7052983</v>
+        <v>7053074</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4222,6 +4234,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Bohål ca 3 m upp i granhögstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4510,10 +4527,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130741290</v>
+        <v>130741313</v>
       </c>
       <c r="B34" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4521,42 +4538,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444005</v>
+        <v>443985</v>
       </c>
       <c r="R34" t="n">
-        <v>7053074</v>
+        <v>7052983</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4589,11 +4594,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Bohål ca 3 m upp i granhögstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5222,7 +5222,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130734173</v>
+        <v>130741318</v>
       </c>
       <c r="B40" t="n">
         <v>79221</v>
@@ -5251,19 +5251,16 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444046</v>
+        <v>444153</v>
       </c>
       <c r="R40" t="n">
-        <v>7053496</v>
+        <v>7053487</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5298,65 +5295,34 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På grenar av en stående död gran med full längd och 36 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130741295</v>
+        <v>130734173</v>
       </c>
       <c r="B41" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5364,34 +5330,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>443845</v>
+        <v>444046</v>
       </c>
       <c r="R41" t="n">
-        <v>7052918</v>
+        <v>7053496</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5428,7 +5397,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På grenar av en stående död gran med full längd och 36 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5437,25 +5406,51 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130741301</v>
+        <v>130741295</v>
       </c>
       <c r="B42" t="n">
         <v>57864</v>
@@ -5490,10 +5485,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443990</v>
+        <v>443845</v>
       </c>
       <c r="R42" t="n">
-        <v>7052974</v>
+        <v>7052918</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5530,7 +5525,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5557,7 +5552,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130741292</v>
+        <v>130741301</v>
       </c>
       <c r="B43" t="n">
         <v>57864</v>
@@ -5592,10 +5587,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443750</v>
+        <v>443990</v>
       </c>
       <c r="R43" t="n">
-        <v>7052993</v>
+        <v>7052974</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5632,7 +5627,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5659,7 +5654,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130734144</v>
+        <v>130741292</v>
       </c>
       <c r="B44" t="n">
         <v>57864</v>
@@ -5688,24 +5683,16 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>444016</v>
+        <v>443750</v>
       </c>
       <c r="R44" t="n">
-        <v>7053579</v>
+        <v>7052993</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5742,7 +5729,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på stambasen av en gran.</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5753,51 +5740,26 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130741318</v>
+        <v>130734144</v>
       </c>
       <c r="B45" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5805,34 +5767,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444153</v>
+        <v>444016</v>
       </c>
       <c r="R45" t="n">
-        <v>7053487</v>
+        <v>7053579</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5867,6 +5837,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack, färska, på stambasen av en gran.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5875,16 +5850,41 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6738,10 +6738,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130734167</v>
+        <v>130741311</v>
       </c>
       <c r="B53" t="n">
-        <v>79221</v>
+        <v>91796</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6749,37 +6749,30 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444319</v>
+        <v>443991</v>
       </c>
       <c r="R53" t="n">
-        <v>7054017</v>
+        <v>7052955</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6814,62 +6807,31 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130741316</v>
+        <v>130734167</v>
       </c>
       <c r="B54" t="n">
         <v>79221</v>
@@ -6898,16 +6860,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444000</v>
+        <v>444319</v>
       </c>
       <c r="R54" t="n">
-        <v>7053558</v>
+        <v>7054017</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6944,7 +6909,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6953,28 +6918,54 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130741311</v>
+        <v>130741316</v>
       </c>
       <c r="B55" t="n">
-        <v>91796</v>
+        <v>79221</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6982,19 +6973,23 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -7002,10 +6997,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443991</v>
+        <v>444000</v>
       </c>
       <c r="R55" t="n">
-        <v>7052955</v>
+        <v>7053558</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7038,6 +7033,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7166,7 +7166,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130741309</v>
+        <v>130741310</v>
       </c>
       <c r="B57" t="n">
         <v>91796</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443836</v>
+        <v>443891</v>
       </c>
       <c r="R57" t="n">
-        <v>7052967</v>
+        <v>7053029</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7259,7 +7259,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130741310</v>
+        <v>130741309</v>
       </c>
       <c r="B58" t="n">
         <v>91796</v>
@@ -7290,10 +7290,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443891</v>
+        <v>443836</v>
       </c>
       <c r="R58" t="n">
-        <v>7053029</v>
+        <v>7052967</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7915,7 +7915,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130734179</v>
+        <v>130734172</v>
       </c>
       <c r="B64" t="n">
         <v>79221</v>
@@ -7953,10 +7953,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>443901</v>
+        <v>444002</v>
       </c>
       <c r="R64" t="n">
-        <v>7053212</v>
+        <v>7053503</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8041,7 +8041,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130734172</v>
+        <v>130734179</v>
       </c>
       <c r="B65" t="n">
         <v>79221</v>
@@ -8079,10 +8079,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>444002</v>
+        <v>443901</v>
       </c>
       <c r="R65" t="n">
-        <v>7053503</v>
+        <v>7053212</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>

--- a/artfynd/A 61382-2025 artfynd.xlsx
+++ b/artfynd/A 61382-2025 artfynd.xlsx
@@ -1690,7 +1690,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130734145</v>
+        <v>130741302</v>
       </c>
       <c r="B10" t="n">
         <v>57864</v>
@@ -1719,24 +1719,16 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443967</v>
+        <v>443997</v>
       </c>
       <c r="R10" t="n">
-        <v>7053469</v>
+        <v>7053008</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1773,7 +1765,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1784,53 +1776,23 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog.</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130741302</v>
+        <v>130741291</v>
       </c>
       <c r="B11" t="n">
         <v>57864</v>
@@ -1865,10 +1827,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443997</v>
+        <v>443794</v>
       </c>
       <c r="R11" t="n">
-        <v>7053008</v>
+        <v>7053002</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1905,7 +1867,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1932,7 +1894,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130741291</v>
+        <v>130734145</v>
       </c>
       <c r="B12" t="n">
         <v>57864</v>
@@ -1961,16 +1923,24 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443794</v>
+        <v>443967</v>
       </c>
       <c r="R12" t="n">
-        <v>7053002</v>
+        <v>7053469</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2007,7 +1977,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2018,16 +1988,46 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog.</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130734150</v>
+        <v>130734162</v>
       </c>
       <c r="B23" t="n">
-        <v>80327</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,30 +3239,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3270,10 +3266,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444358</v>
+        <v>444375</v>
       </c>
       <c r="R23" t="n">
-        <v>7054049</v>
+        <v>7054118</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3308,11 +3304,6 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gott om bålar av skrovellav på en hyfsat grov sälg.</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3328,29 +3319,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med björk och inslag av sälg.</t>
-        </is>
-      </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
@@ -3461,7 +3447,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130734162</v>
+        <v>130734165</v>
       </c>
       <c r="B25" t="n">
         <v>79221</v>
@@ -3499,10 +3485,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444375</v>
+        <v>444343</v>
       </c>
       <c r="R25" t="n">
-        <v>7054118</v>
+        <v>7054057</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3535,6 +3521,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3587,7 +3578,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130734165</v>
+        <v>130734185</v>
       </c>
       <c r="B26" t="n">
         <v>79221</v>
@@ -3625,10 +3616,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444343</v>
+        <v>444157</v>
       </c>
       <c r="R26" t="n">
-        <v>7054057</v>
+        <v>7053507</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3665,7 +3656,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3718,10 +3709,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130734185</v>
+        <v>130734150</v>
       </c>
       <c r="B27" t="n">
-        <v>79221</v>
+        <v>80327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3729,26 +3720,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3756,10 +3751,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444157</v>
+        <v>444358</v>
       </c>
       <c r="R27" t="n">
-        <v>7053507</v>
+        <v>7054049</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3796,7 +3791,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Gott om bålar av skrovellav på en hyfsat grov sälg.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3814,24 +3809,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med björk och inslag av sälg.</t>
+        </is>
+      </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3849,7 +3849,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130741285</v>
+        <v>130741297</v>
       </c>
       <c r="B28" t="n">
         <v>57864</v>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443963</v>
+        <v>443871</v>
       </c>
       <c r="R28" t="n">
-        <v>7052972</v>
+        <v>7052942</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3924,7 +3924,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4053,7 +4053,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130741297</v>
+        <v>130741285</v>
       </c>
       <c r="B30" t="n">
         <v>57864</v>
@@ -4088,10 +4088,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443871</v>
+        <v>443963</v>
       </c>
       <c r="R30" t="n">
-        <v>7052942</v>
+        <v>7052972</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4155,10 +4155,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130741290</v>
+        <v>130734181</v>
       </c>
       <c r="B31" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4166,42 +4166,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>444005</v>
+        <v>443859</v>
       </c>
       <c r="R31" t="n">
-        <v>7053074</v>
+        <v>7053310</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4238,7 +4233,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Bohål ca 3 m upp i granhögstubbe</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4247,25 +4242,51 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130734181</v>
+        <v>130734178</v>
       </c>
       <c r="B32" t="n">
         <v>79221</v>
@@ -4303,10 +4324,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443859</v>
+        <v>443988</v>
       </c>
       <c r="R32" t="n">
-        <v>7053310</v>
+        <v>7053189</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4343,7 +4364,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>På gammal gran i luckig äldre granskog.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4396,10 +4417,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130734178</v>
+        <v>130741313</v>
       </c>
       <c r="B33" t="n">
-        <v>79221</v>
+        <v>91796</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4407,37 +4428,30 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443988</v>
+        <v>443985</v>
       </c>
       <c r="R33" t="n">
-        <v>7053189</v>
+        <v>7052983</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4472,65 +4486,34 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gammal gran i luckig äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130741313</v>
+        <v>130741290</v>
       </c>
       <c r="B34" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4538,30 +4521,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443985</v>
+        <v>444005</v>
       </c>
       <c r="R34" t="n">
-        <v>7052983</v>
+        <v>7053074</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4594,6 +4589,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Bohål ca 3 m upp i granhögstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5450,7 +5450,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130741295</v>
+        <v>130741292</v>
       </c>
       <c r="B42" t="n">
         <v>57864</v>
@@ -5485,10 +5485,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443845</v>
+        <v>443750</v>
       </c>
       <c r="R42" t="n">
-        <v>7052918</v>
+        <v>7052993</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5654,7 +5654,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130741292</v>
+        <v>130741295</v>
       </c>
       <c r="B44" t="n">
         <v>57864</v>
@@ -5689,10 +5689,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443750</v>
+        <v>443845</v>
       </c>
       <c r="R44" t="n">
-        <v>7052993</v>
+        <v>7052918</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6264,7 +6264,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130734146</v>
+        <v>130741288</v>
       </c>
       <c r="B49" t="n">
         <v>57864</v>
@@ -6293,24 +6293,16 @@
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443949</v>
+        <v>443996</v>
       </c>
       <c r="R49" t="n">
-        <v>7053197</v>
+        <v>7053048</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6347,7 +6339,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på stambasen av en gammal gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6358,48 +6350,23 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130734148</v>
+        <v>130741299</v>
       </c>
       <c r="B50" t="n">
         <v>57864</v>
@@ -6428,24 +6395,16 @@
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>444153</v>
+        <v>443972</v>
       </c>
       <c r="R50" t="n">
-        <v>7053496</v>
+        <v>7052967</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6482,7 +6441,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och ev. något färskt, på stambasen av en gran. Medelhögt till högt livsmiljövärde på fyndplatsen baserat på volym stående död ved av gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6493,48 +6452,23 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130741288</v>
+        <v>130734148</v>
       </c>
       <c r="B51" t="n">
         <v>57864</v>
@@ -6563,16 +6497,24 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>443996</v>
+        <v>444153</v>
       </c>
       <c r="R51" t="n">
-        <v>7053048</v>
+        <v>7053496</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6609,7 +6551,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, äldre och ev. något färskt, på stambasen av en gran. Medelhögt till högt livsmiljövärde på fyndplatsen baserat på volym stående död ved av gran.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6620,23 +6562,48 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130741299</v>
+        <v>130734146</v>
       </c>
       <c r="B52" t="n">
         <v>57864</v>
@@ -6665,16 +6632,24 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443972</v>
+        <v>443949</v>
       </c>
       <c r="R52" t="n">
-        <v>7052967</v>
+        <v>7053197</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6711,7 +6686,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska, enstaka på stambasen av en gammal gran.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6722,26 +6697,51 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130741311</v>
+        <v>130734167</v>
       </c>
       <c r="B53" t="n">
-        <v>91796</v>
+        <v>79221</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6749,30 +6749,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>443991</v>
+        <v>444319</v>
       </c>
       <c r="R53" t="n">
-        <v>7052955</v>
+        <v>7054017</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6807,34 +6814,65 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130734167</v>
+        <v>130741311</v>
       </c>
       <c r="B54" t="n">
-        <v>79221</v>
+        <v>91796</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6842,37 +6880,30 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>444319</v>
+        <v>443991</v>
       </c>
       <c r="R54" t="n">
-        <v>7054017</v>
+        <v>7052955</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6907,55 +6938,24 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>På flera granar.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -7483,7 +7483,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130741298</v>
+        <v>130741287</v>
       </c>
       <c r="B60" t="n">
         <v>57864</v>
@@ -7518,10 +7518,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443946</v>
+        <v>444000</v>
       </c>
       <c r="R60" t="n">
-        <v>7052921</v>
+        <v>7053028</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7585,7 +7585,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130741287</v>
+        <v>130741298</v>
       </c>
       <c r="B61" t="n">
         <v>57864</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>444000</v>
+        <v>443946</v>
       </c>
       <c r="R61" t="n">
-        <v>7053028</v>
+        <v>7052921</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>

--- a/artfynd/A 61382-2025 artfynd.xlsx
+++ b/artfynd/A 61382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130734182</v>
+        <v>130741286</v>
       </c>
       <c r="B2" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,50 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443903</v>
+        <v>443968</v>
       </c>
       <c r="R2" t="n">
-        <v>7053286</v>
+        <v>7052990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +766,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog.</t>
+          <t>Avbarkade en något klen gran</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,51 +775,25 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130734186</v>
+        <v>130734182</v>
       </c>
       <c r="B3" t="n">
         <v>79221</v>
@@ -844,10 +831,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444272</v>
+        <v>443903</v>
       </c>
       <c r="R3" t="n">
-        <v>7053547</v>
+        <v>7053286</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +871,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar i senvuxen äldre granskog.</t>
+          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,10 +924,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130741286</v>
+        <v>130734186</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,50 +935,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443968</v>
+        <v>444272</v>
       </c>
       <c r="R4" t="n">
-        <v>7052990</v>
+        <v>7053547</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,7 +1002,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Avbarkade en något klen gran</t>
+          <t>Rikligt med garnlav på flera granar i senvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,28 +1011,54 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130734193</v>
+        <v>130734153</v>
       </c>
       <c r="B5" t="n">
-        <v>79221</v>
+        <v>91772</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,26 +1066,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1093,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444436</v>
+        <v>443857</v>
       </c>
       <c r="R5" t="n">
-        <v>7053798</v>
+        <v>7053224</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,6 +1135,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gott om fruktkroppar i stambasen av en stående grov gran med 50 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1148,7 +1157,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
+          <t>Flerskiktad äldre granskog med inslag av björk och enstaka asp.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1163,12 +1172,12 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1186,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130734153</v>
+        <v>130734193</v>
       </c>
       <c r="B6" t="n">
-        <v>91772</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,30 +1206,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1228,10 +1233,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443857</v>
+        <v>444436</v>
       </c>
       <c r="R6" t="n">
-        <v>7053224</v>
+        <v>7053798</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,11 +1271,6 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i stambasen av en stående grov gran med 50 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Flerskiktad äldre granskog med inslag av björk och enstaka asp.</t>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1303,12 +1303,12 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -3228,10 +3228,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130734162</v>
+        <v>130741297</v>
       </c>
       <c r="B23" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,37 +3239,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444375</v>
+        <v>443871</v>
       </c>
       <c r="R23" t="n">
-        <v>7054118</v>
+        <v>7052942</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3304,60 +3301,39 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130741314</v>
+        <v>130741282</v>
       </c>
       <c r="B24" t="n">
-        <v>91796</v>
+        <v>57864</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3365,19 +3341,23 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3385,10 +3365,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444416</v>
+        <v>443897</v>
       </c>
       <c r="R24" t="n">
-        <v>7053728</v>
+        <v>7052981</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3421,6 +3401,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3447,10 +3432,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130734165</v>
+        <v>130741285</v>
       </c>
       <c r="B25" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3458,37 +3443,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>444343</v>
+        <v>443963</v>
       </c>
       <c r="R25" t="n">
-        <v>7054057</v>
+        <v>7052972</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3525,7 +3507,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3534,54 +3516,28 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130734185</v>
+        <v>130734150</v>
       </c>
       <c r="B26" t="n">
-        <v>79221</v>
+        <v>80327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3589,26 +3545,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3616,10 +3576,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444157</v>
+        <v>444358</v>
       </c>
       <c r="R26" t="n">
-        <v>7053507</v>
+        <v>7054049</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3656,7 +3616,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Gott om bålar av skrovellav på en hyfsat grov sälg.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3674,24 +3634,29 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med björk och inslag av sälg.</t>
+        </is>
+      </c>
       <c r="AJ26" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3709,10 +3674,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130734150</v>
+        <v>130734162</v>
       </c>
       <c r="B27" t="n">
-        <v>80327</v>
+        <v>79221</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3720,30 +3685,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3751,10 +3712,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>444358</v>
+        <v>444375</v>
       </c>
       <c r="R27" t="n">
-        <v>7054049</v>
+        <v>7054118</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3789,11 +3750,6 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Gott om bålar av skrovellav på en hyfsat grov sälg.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3809,29 +3765,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med björk och inslag av sälg.</t>
-        </is>
-      </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3849,10 +3800,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130741297</v>
+        <v>130741314</v>
       </c>
       <c r="B28" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,23 +3811,19 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3884,10 +3831,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>443871</v>
+        <v>444416</v>
       </c>
       <c r="R28" t="n">
-        <v>7052942</v>
+        <v>7053728</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3920,11 +3867,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3951,10 +3893,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130741282</v>
+        <v>130734165</v>
       </c>
       <c r="B29" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3962,34 +3904,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>443897</v>
+        <v>444343</v>
       </c>
       <c r="R29" t="n">
-        <v>7052981</v>
+        <v>7054057</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4026,7 +3971,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4035,28 +3980,54 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130741285</v>
+        <v>130734185</v>
       </c>
       <c r="B30" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4064,34 +4035,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>443963</v>
+        <v>444157</v>
       </c>
       <c r="R30" t="n">
-        <v>7052972</v>
+        <v>7053507</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4128,7 +4102,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4137,18 +4111,44 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -8269,10 +8269,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130734184</v>
+        <v>130741280</v>
       </c>
       <c r="B67" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8280,37 +8280,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444032</v>
+        <v>444040</v>
       </c>
       <c r="R67" t="n">
-        <v>7053290</v>
+        <v>7053449</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8347,7 +8344,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Garnlav på en tydligt gammal gran i gles senvuxen granskog.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8356,51 +8353,25 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130734188</v>
+        <v>130734184</v>
       </c>
       <c r="B68" t="n">
         <v>79221</v>
@@ -8438,10 +8409,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444304</v>
+        <v>444032</v>
       </c>
       <c r="R68" t="n">
-        <v>7053564</v>
+        <v>7053290</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8478,7 +8449,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Växer på en tydligt gammal gran i relativt senvuxen gles granskog.</t>
+          <t>Garnlav på en tydligt gammal gran i gles senvuxen granskog.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8531,7 +8502,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130734191</v>
+        <v>130734188</v>
       </c>
       <c r="B69" t="n">
         <v>79221</v>
@@ -8569,10 +8540,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444407</v>
+        <v>444304</v>
       </c>
       <c r="R69" t="n">
-        <v>7053726</v>
+        <v>7053564</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8609,7 +8580,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på gran.</t>
+          <t>Växer på en tydligt gammal gran i relativt senvuxen gles granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8625,11 +8596,6 @@
       <c r="AH69" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI69" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ69" t="inlineStr">
@@ -8667,7 +8633,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130734168</v>
+        <v>130734191</v>
       </c>
       <c r="B70" t="n">
         <v>79221</v>
@@ -8705,10 +8671,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444293</v>
+        <v>444407</v>
       </c>
       <c r="R70" t="n">
-        <v>7054016</v>
+        <v>7053726</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8743,6 +8709,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med garnlav på gran.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8756,6 +8727,11 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI70" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -8793,7 +8769,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130734169</v>
+        <v>130734168</v>
       </c>
       <c r="B71" t="n">
         <v>79221</v>
@@ -8831,10 +8807,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444160</v>
+        <v>444293</v>
       </c>
       <c r="R71" t="n">
-        <v>7053858</v>
+        <v>7054016</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8867,11 +8843,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8924,7 +8895,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130734183</v>
+        <v>130734169</v>
       </c>
       <c r="B72" t="n">
         <v>79221</v>
@@ -8962,10 +8933,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>443986</v>
+        <v>444160</v>
       </c>
       <c r="R72" t="n">
-        <v>7053263</v>
+        <v>7053858</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9002,7 +8973,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gran i gles senvuxen granskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9018,11 +8989,6 @@
       <c r="AH72" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med björk och inslag av asp.</t>
         </is>
       </c>
       <c r="AJ72" t="inlineStr">
@@ -9060,10 +9026,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130734151</v>
+        <v>130734183</v>
       </c>
       <c r="B73" t="n">
-        <v>80327</v>
+        <v>79221</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9071,21 +9037,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -9098,10 +9064,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>444218</v>
+        <v>443986</v>
       </c>
       <c r="R73" t="n">
-        <v>7053557</v>
+        <v>7053263</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9138,7 +9104,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Växer på en levande skadad sälg.</t>
+          <t>På gran i gles senvuxen granskog.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9158,27 +9124,27 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Flerskiktad äldre granskog med inslag av björk och enstaka sälg.</t>
+          <t>Grandominerad skog med björk och inslag av asp.</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK73" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM73" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -9196,10 +9162,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130741280</v>
+        <v>130734151</v>
       </c>
       <c r="B74" t="n">
-        <v>57864</v>
+        <v>80327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9207,34 +9173,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444040</v>
+        <v>444218</v>
       </c>
       <c r="R74" t="n">
-        <v>7053449</v>
+        <v>7053557</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9271,7 +9240,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Växer på en levande skadad sälg.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9280,18 +9249,49 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI74" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av björk och enstaka sälg.</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>

--- a/artfynd/A 61382-2025 artfynd.xlsx
+++ b/artfynd/A 61382-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130741286</v>
+        <v>130734182</v>
       </c>
       <c r="B2" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,50 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443968</v>
+        <v>443903</v>
       </c>
       <c r="R2" t="n">
-        <v>7052990</v>
+        <v>7053286</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,7 +753,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Avbarkade en något klen gran</t>
+          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,25 +762,51 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130734182</v>
+        <v>130734186</v>
       </c>
       <c r="B3" t="n">
         <v>79221</v>
@@ -831,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443903</v>
+        <v>444272</v>
       </c>
       <c r="R3" t="n">
-        <v>7053286</v>
+        <v>7053547</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +884,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På gran i äldre granskog.</t>
+          <t>Rikligt med garnlav på flera granar i senvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,10 +937,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130734186</v>
+        <v>130741286</v>
       </c>
       <c r="B4" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,37 +948,50 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>444272</v>
+        <v>443968</v>
       </c>
       <c r="R4" t="n">
-        <v>7053547</v>
+        <v>7052990</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,7 +1028,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar i senvuxen äldre granskog.</t>
+          <t>Avbarkade en något klen gran</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,44 +1037,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -2131,10 +2131,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130734180</v>
+        <v>130741279</v>
       </c>
       <c r="B14" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2142,37 +2142,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>443846</v>
+        <v>444007</v>
       </c>
       <c r="R14" t="n">
-        <v>7053252</v>
+        <v>7053457</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2209,7 +2206,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Växer på grenar av en stående död gran med full längd (bhd ca 30 cm).</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2218,51 +2215,25 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130734170</v>
+        <v>130734180</v>
       </c>
       <c r="B15" t="n">
         <v>79221</v>
@@ -2300,10 +2271,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>444133</v>
+        <v>443846</v>
       </c>
       <c r="R15" t="n">
-        <v>7053693</v>
+        <v>7053252</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2338,6 +2309,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Växer på grenar av en stående död gran med full längd (bhd ca 30 cm).</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2365,12 +2341,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2388,7 +2364,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130734164</v>
+        <v>130734170</v>
       </c>
       <c r="B16" t="n">
         <v>79221</v>
@@ -2426,10 +2402,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444362</v>
+        <v>444133</v>
       </c>
       <c r="R16" t="n">
-        <v>7054079</v>
+        <v>7053693</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2462,11 +2438,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>På gamla granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2519,10 +2490,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130741279</v>
+        <v>130734164</v>
       </c>
       <c r="B17" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2530,34 +2501,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444007</v>
+        <v>444362</v>
       </c>
       <c r="R17" t="n">
-        <v>7053457</v>
+        <v>7054079</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2594,7 +2568,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gamla granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2603,18 +2577,44 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130734190</v>
+        <v>130741284</v>
       </c>
       <c r="B19" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2734,37 +2734,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>444347</v>
+        <v>443929</v>
       </c>
       <c r="R19" t="n">
-        <v>7053668</v>
+        <v>7052944</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2801,7 +2798,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Garnlav på en stående död gran med full längd och ca 10-20 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2810,56 +2807,25 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130734177</v>
+        <v>130734190</v>
       </c>
       <c r="B20" t="n">
         <v>79221</v>
@@ -2897,10 +2863,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>443938</v>
+        <v>444347</v>
       </c>
       <c r="R20" t="n">
-        <v>7053186</v>
+        <v>7053668</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2937,7 +2903,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran i gammal granskog.</t>
+          <t>Garnlav på en stående död gran med full längd och ca 10-20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2955,6 +2921,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
+        </is>
+      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2967,12 +2938,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2990,7 +2961,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130734192</v>
+        <v>130734177</v>
       </c>
       <c r="B21" t="n">
         <v>79221</v>
@@ -3028,10 +2999,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>444423</v>
+        <v>443938</v>
       </c>
       <c r="R21" t="n">
-        <v>7053773</v>
+        <v>7053186</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3068,7 +3039,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt med garnlavsbålar på flera granar.</t>
+          <t>På gran i gammal granskog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3084,11 +3055,6 @@
       <c r="AH21" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
@@ -3126,10 +3092,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130741284</v>
+        <v>130734192</v>
       </c>
       <c r="B22" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3137,34 +3103,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>443929</v>
+        <v>444423</v>
       </c>
       <c r="R22" t="n">
-        <v>7052944</v>
+        <v>7053773</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3201,7 +3170,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Måttligt till rikligt med garnlavsbålar på flera granar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3210,28 +3179,59 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130741297</v>
+        <v>130734150</v>
       </c>
       <c r="B23" t="n">
-        <v>57864</v>
+        <v>80327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3239,34 +3239,41 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>443871</v>
+        <v>444358</v>
       </c>
       <c r="R23" t="n">
-        <v>7052942</v>
+        <v>7054049</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3303,7 +3310,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gott om bålar av skrovellav på en hyfsat grov sälg.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3312,25 +3319,56 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre grandominerad skog med björk och inslag av sälg.</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130741282</v>
+        <v>130741297</v>
       </c>
       <c r="B24" t="n">
         <v>57864</v>
@@ -3365,10 +3403,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>443897</v>
+        <v>443871</v>
       </c>
       <c r="R24" t="n">
-        <v>7052981</v>
+        <v>7052942</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3405,7 +3443,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3432,7 +3470,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130741285</v>
+        <v>130741282</v>
       </c>
       <c r="B25" t="n">
         <v>57864</v>
@@ -3467,10 +3505,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443963</v>
+        <v>443897</v>
       </c>
       <c r="R25" t="n">
-        <v>7052972</v>
+        <v>7052981</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3534,10 +3572,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130734150</v>
+        <v>130741285</v>
       </c>
       <c r="B26" t="n">
-        <v>80327</v>
+        <v>57864</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3545,41 +3583,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>444358</v>
+        <v>443963</v>
       </c>
       <c r="R26" t="n">
-        <v>7054049</v>
+        <v>7052972</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3616,7 +3647,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Gott om bålar av skrovellav på en hyfsat grov sälg.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3625,49 +3656,18 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med björk och inslag av sälg.</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -4155,10 +4155,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130734181</v>
+        <v>130741290</v>
       </c>
       <c r="B31" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4166,37 +4166,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443859</v>
+        <v>444005</v>
       </c>
       <c r="R31" t="n">
-        <v>7053310</v>
+        <v>7053074</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4233,7 +4238,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Bohål ca 3 m upp i granhögstubbe</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4242,51 +4247,25 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130734178</v>
+        <v>130734181</v>
       </c>
       <c r="B32" t="n">
         <v>79221</v>
@@ -4324,10 +4303,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>443988</v>
+        <v>443859</v>
       </c>
       <c r="R32" t="n">
-        <v>7053189</v>
+        <v>7053310</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4364,7 +4343,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>På gammal gran i luckig äldre granskog.</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4417,10 +4396,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130741313</v>
+        <v>130734178</v>
       </c>
       <c r="B33" t="n">
-        <v>91796</v>
+        <v>79221</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4428,30 +4407,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443985</v>
+        <v>443988</v>
       </c>
       <c r="R33" t="n">
-        <v>7052983</v>
+        <v>7053189</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4486,34 +4472,65 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gammal gran i luckig äldre granskog.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130741290</v>
+        <v>130741313</v>
       </c>
       <c r="B34" t="n">
-        <v>57864</v>
+        <v>91796</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4521,42 +4538,30 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>444005</v>
+        <v>443985</v>
       </c>
       <c r="R34" t="n">
-        <v>7053074</v>
+        <v>7052983</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4589,11 +4594,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Bohål ca 3 m upp i granhögstubbe</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5222,10 +5222,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130741318</v>
+        <v>130741292</v>
       </c>
       <c r="B40" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5233,21 +5233,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5257,10 +5257,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444153</v>
+        <v>443750</v>
       </c>
       <c r="R40" t="n">
-        <v>7053487</v>
+        <v>7052993</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5293,6 +5293,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5319,10 +5324,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130734173</v>
+        <v>130741301</v>
       </c>
       <c r="B41" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5330,37 +5335,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444046</v>
+        <v>443990</v>
       </c>
       <c r="R41" t="n">
-        <v>7053496</v>
+        <v>7052974</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5397,7 +5399,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På grenar av en stående död gran med full längd och 36 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5406,51 +5408,25 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130741292</v>
+        <v>130741295</v>
       </c>
       <c r="B42" t="n">
         <v>57864</v>
@@ -5485,10 +5461,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443750</v>
+        <v>443845</v>
       </c>
       <c r="R42" t="n">
-        <v>7052993</v>
+        <v>7052918</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5525,7 +5501,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5552,7 +5528,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130741301</v>
+        <v>130734144</v>
       </c>
       <c r="B43" t="n">
         <v>57864</v>
@@ -5581,16 +5557,24 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443990</v>
+        <v>444016</v>
       </c>
       <c r="R43" t="n">
-        <v>7052974</v>
+        <v>7053579</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5627,7 +5611,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5638,26 +5622,51 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130741295</v>
+        <v>130741318</v>
       </c>
       <c r="B44" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5665,21 +5674,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5689,10 +5698,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443845</v>
+        <v>444153</v>
       </c>
       <c r="R44" t="n">
-        <v>7052918</v>
+        <v>7053487</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5725,11 +5734,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5756,10 +5760,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130734144</v>
+        <v>130734173</v>
       </c>
       <c r="B45" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5767,31 +5771,26 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
@@ -5799,10 +5798,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444016</v>
+        <v>444046</v>
       </c>
       <c r="R45" t="n">
-        <v>7053579</v>
+        <v>7053496</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5839,7 +5838,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på stambasen av en gran.</t>
+          <t>På grenar av en stående död gran med full längd och 36 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5848,6 +5847,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -6738,10 +6738,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130734167</v>
+        <v>130741293</v>
       </c>
       <c r="B53" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6749,37 +6749,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444319</v>
+        <v>443827</v>
       </c>
       <c r="R53" t="n">
-        <v>7054017</v>
+        <v>7052932</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6816,7 +6813,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6825,54 +6822,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130741311</v>
+        <v>130734167</v>
       </c>
       <c r="B54" t="n">
-        <v>91796</v>
+        <v>79221</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6880,30 +6851,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>443991</v>
+        <v>444319</v>
       </c>
       <c r="R54" t="n">
-        <v>7052955</v>
+        <v>7054017</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6938,34 +6916,65 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På flera granar.</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130741316</v>
+        <v>130741311</v>
       </c>
       <c r="B55" t="n">
-        <v>79221</v>
+        <v>91796</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6973,23 +6982,19 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6997,10 +7002,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>444000</v>
+        <v>443991</v>
       </c>
       <c r="R55" t="n">
-        <v>7053558</v>
+        <v>7052955</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7033,11 +7038,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7064,10 +7064,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130741293</v>
+        <v>130741316</v>
       </c>
       <c r="B56" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7075,21 +7075,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -7099,10 +7099,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443827</v>
+        <v>444000</v>
       </c>
       <c r="R56" t="n">
-        <v>7052932</v>
+        <v>7053558</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7687,10 +7687,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130734155</v>
+        <v>130741283</v>
       </c>
       <c r="B62" t="n">
-        <v>91772</v>
+        <v>57864</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7698,41 +7698,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>443861</v>
+        <v>443927</v>
       </c>
       <c r="R62" t="n">
-        <v>7053306</v>
+        <v>7052967</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7769,7 +7762,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en levande relativt grov gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7778,54 +7771,28 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130741308</v>
+        <v>130734155</v>
       </c>
       <c r="B63" t="n">
-        <v>91796</v>
+        <v>91772</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7833,30 +7800,41 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>444020</v>
+        <v>443861</v>
       </c>
       <c r="R63" t="n">
-        <v>7053458</v>
+        <v>7053306</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7891,34 +7869,65 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i stambasen av en levande relativt grov gran.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130734172</v>
+        <v>130741308</v>
       </c>
       <c r="B64" t="n">
-        <v>79221</v>
+        <v>91796</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7926,37 +7935,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444002</v>
+        <v>444020</v>
       </c>
       <c r="R64" t="n">
-        <v>7053503</v>
+        <v>7053458</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7997,51 +7999,25 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130734179</v>
+        <v>130734172</v>
       </c>
       <c r="B65" t="n">
         <v>79221</v>
@@ -8079,10 +8055,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443901</v>
+        <v>444002</v>
       </c>
       <c r="R65" t="n">
-        <v>7053212</v>
+        <v>7053503</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8167,10 +8143,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130741283</v>
+        <v>130734179</v>
       </c>
       <c r="B66" t="n">
-        <v>57864</v>
+        <v>79221</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8178,34 +8154,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443927</v>
+        <v>443901</v>
       </c>
       <c r="R66" t="n">
-        <v>7052967</v>
+        <v>7053212</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8240,39 +8219,60 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130741280</v>
+        <v>130734151</v>
       </c>
       <c r="B67" t="n">
-        <v>57864</v>
+        <v>80327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8280,34 +8280,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444040</v>
+        <v>444218</v>
       </c>
       <c r="R67" t="n">
-        <v>7053449</v>
+        <v>7053557</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8344,7 +8347,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Växer på en levande skadad sälg.</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8353,28 +8356,59 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI67" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av björk och enstaka sälg.</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130734184</v>
+        <v>130741280</v>
       </c>
       <c r="B68" t="n">
-        <v>79221</v>
+        <v>57864</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8382,37 +8416,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>444032</v>
+        <v>444040</v>
       </c>
       <c r="R68" t="n">
-        <v>7053290</v>
+        <v>7053449</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8449,7 +8480,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Garnlav på en tydligt gammal gran i gles senvuxen granskog.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8458,51 +8489,25 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130734188</v>
+        <v>130734184</v>
       </c>
       <c r="B69" t="n">
         <v>79221</v>
@@ -8540,10 +8545,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>444304</v>
+        <v>444032</v>
       </c>
       <c r="R69" t="n">
-        <v>7053564</v>
+        <v>7053290</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8580,7 +8585,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Växer på en tydligt gammal gran i relativt senvuxen gles granskog.</t>
+          <t>Garnlav på en tydligt gammal gran i gles senvuxen granskog.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8633,7 +8638,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130734191</v>
+        <v>130734188</v>
       </c>
       <c r="B70" t="n">
         <v>79221</v>
@@ -8671,10 +8676,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>444407</v>
+        <v>444304</v>
       </c>
       <c r="R70" t="n">
-        <v>7053726</v>
+        <v>7053564</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8711,7 +8716,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Relativt rikligt med garnlav på gran.</t>
+          <t>Växer på en tydligt gammal gran i relativt senvuxen gles granskog.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8727,11 +8732,6 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI70" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ70" t="inlineStr">
@@ -8769,7 +8769,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130734168</v>
+        <v>130734191</v>
       </c>
       <c r="B71" t="n">
         <v>79221</v>
@@ -8807,10 +8807,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>444293</v>
+        <v>444407</v>
       </c>
       <c r="R71" t="n">
-        <v>7054016</v>
+        <v>7053726</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8845,6 +8845,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Relativt rikligt med garnlav på gran.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8858,6 +8863,11 @@
       <c r="AH71" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI71" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ71" t="inlineStr">
@@ -8895,7 +8905,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>130734169</v>
+        <v>130734168</v>
       </c>
       <c r="B72" t="n">
         <v>79221</v>
@@ -8933,10 +8943,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>444160</v>
+        <v>444293</v>
       </c>
       <c r="R72" t="n">
-        <v>7053858</v>
+        <v>7054016</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8969,11 +8979,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9026,7 +9031,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130734183</v>
+        <v>130734169</v>
       </c>
       <c r="B73" t="n">
         <v>79221</v>
@@ -9064,10 +9069,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>443986</v>
+        <v>444160</v>
       </c>
       <c r="R73" t="n">
-        <v>7053263</v>
+        <v>7053858</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9104,7 +9109,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På gran i gles senvuxen granskog.</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9120,11 +9125,6 @@
       <c r="AH73" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med björk och inslag av asp.</t>
         </is>
       </c>
       <c r="AJ73" t="inlineStr">
@@ -9162,10 +9162,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130734151</v>
+        <v>130734183</v>
       </c>
       <c r="B74" t="n">
-        <v>80327</v>
+        <v>79221</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9173,21 +9173,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -9200,10 +9200,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>444218</v>
+        <v>443986</v>
       </c>
       <c r="R74" t="n">
-        <v>7053557</v>
+        <v>7053263</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9240,7 +9240,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Växer på en levande skadad sälg.</t>
+          <t>På gran i gles senvuxen granskog.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9260,27 +9260,27 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Flerskiktad äldre granskog med inslag av björk och enstaka sälg.</t>
+          <t>Grandominerad skog med björk och inslag av asp.</t>
         </is>
       </c>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>

--- a/artfynd/A 61382-2025 artfynd.xlsx
+++ b/artfynd/A 61382-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY74"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130734182</v>
+        <v>130741320</v>
       </c>
       <c r="B2" t="n">
-        <v>79243</v>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443903</v>
+        <v>444326</v>
       </c>
       <c r="R2" t="n">
-        <v>7053286</v>
+        <v>7053588</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,65 +748,34 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På gran i äldre granskog.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130734186</v>
+        <v>130734153</v>
       </c>
       <c r="B3" t="n">
-        <v>79243</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,26 +783,30 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -844,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>444272</v>
+        <v>443857</v>
       </c>
       <c r="R3" t="n">
-        <v>7053547</v>
+        <v>7053224</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +854,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav på flera granar i senvuxen äldre granskog.</t>
+          <t>Gott om fruktkroppar i stambasen av en stående grov gran med 50 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,6 +872,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Flerskiktad äldre granskog med inslag av björk och enstaka asp.</t>
+        </is>
+      </c>
       <c r="AJ3" t="inlineStr">
         <is>
           <t>gran</t>
@@ -914,12 +889,12 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -937,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130741286</v>
+        <v>130734155</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,50 +923,41 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443968</v>
+        <v>443861</v>
       </c>
       <c r="R4" t="n">
-        <v>7052990</v>
+        <v>7053306</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1028,7 +994,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Avbarkade en något klen gran</t>
+          <t>Flera fruktkroppar i stambasen av en levande relativt grov gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,28 +1003,54 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130734193</v>
+        <v>130734150</v>
       </c>
       <c r="B5" t="n">
-        <v>79243</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,26 +1058,30 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1093,10 +1089,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>444436</v>
+        <v>444358</v>
       </c>
       <c r="R5" t="n">
-        <v>7053798</v>
+        <v>7054049</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,6 +1127,11 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Gott om bålar av skrovellav på en hyfsat grov sälg.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1148,27 +1149,27 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
+          <t>Flerskiktad äldre grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1186,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130734153</v>
+        <v>130734151</v>
       </c>
       <c r="B6" t="n">
-        <v>91804</v>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1197,30 +1198,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1228,10 +1225,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443857</v>
+        <v>444218</v>
       </c>
       <c r="R6" t="n">
-        <v>7053224</v>
+        <v>7053557</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1268,7 +1265,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Gott om fruktkroppar i stambasen av en stående grov gran med 50 cm i brösthöjdsdiameter.</t>
+          <t>Växer på en levande skadad sälg.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,27 +1285,27 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Flerskiktad äldre granskog med inslag av björk och enstaka asp.</t>
+          <t>Flerskiktad äldre granskog med inslag av björk och enstaka sälg.</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1326,14 +1323,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130741319</v>
+        <v>113995171</v>
       </c>
       <c r="B7" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1355,16 +1352,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Nästsjön ö tångeråsen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>444417</v>
+        <v>444428</v>
       </c>
       <c r="R7" t="n">
-        <v>7053741</v>
+        <v>7053708</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1391,17 +1391,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2024-01-09</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,6 +1410,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1428,14 +1429,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130734175</v>
+        <v>130734162</v>
       </c>
       <c r="B8" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1466,10 +1467,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>444124</v>
+        <v>444375</v>
       </c>
       <c r="R8" t="n">
-        <v>7053447</v>
+        <v>7054118</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1502,11 +1503,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1559,45 +1555,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130741302</v>
+        <v>130734164</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>443997</v>
+        <v>444362</v>
       </c>
       <c r="R9" t="n">
-        <v>7053008</v>
+        <v>7054079</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1634,7 +1633,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>På gamla granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1643,63 +1642,92 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130741291</v>
+        <v>130734165</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>443794</v>
+        <v>444343</v>
       </c>
       <c r="R10" t="n">
-        <v>7053002</v>
+        <v>7054057</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1736,7 +1764,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på flera granar.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,60 +1773,81 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130734145</v>
+        <v>130734167</v>
       </c>
       <c r="B11" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1806,10 +1855,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>443967</v>
+        <v>444319</v>
       </c>
       <c r="R11" t="n">
-        <v>7053469</v>
+        <v>7054017</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1846,7 +1895,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,6 +1904,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1863,11 +1913,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog.</t>
-        </is>
-      </c>
       <c r="AJ11" t="inlineStr">
         <is>
           <t>gran</t>
@@ -1880,12 +1925,12 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1903,37 +1948,37 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130734156</v>
+        <v>130734168</v>
       </c>
       <c r="B12" t="n">
-        <v>91828</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1941,10 +1986,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>443886</v>
+        <v>444293</v>
       </c>
       <c r="R12" t="n">
-        <v>7053279</v>
+        <v>7054016</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1979,11 +2024,6 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gott om fruktkroppar i en granhögstubbe.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2011,12 +2051,12 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2034,45 +2074,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130741320</v>
+        <v>130734169</v>
       </c>
       <c r="B13" t="n">
-        <v>89193</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>444326</v>
+        <v>444160</v>
       </c>
       <c r="R13" t="n">
-        <v>7053588</v>
+        <v>7053858</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2107,69 +2150,103 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på gran.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130741279</v>
+        <v>130734170</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>444007</v>
+        <v>444133</v>
       </c>
       <c r="R14" t="n">
-        <v>7053457</v>
+        <v>7053693</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2204,43 +2281,64 @@
           <t>2026-01-16</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130734180</v>
+        <v>130734171</v>
       </c>
       <c r="B15" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2271,10 +2369,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>443846</v>
+        <v>443981</v>
       </c>
       <c r="R15" t="n">
-        <v>7053252</v>
+        <v>7053488</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2311,7 +2409,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Växer på grenar av en stående död gran med full längd (bhd ca 30 cm).</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2341,12 +2439,12 @@
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2364,14 +2462,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130734170</v>
+        <v>130734172</v>
       </c>
       <c r="B16" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2402,10 +2500,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>444133</v>
+        <v>444002</v>
       </c>
       <c r="R16" t="n">
-        <v>7053693</v>
+        <v>7053503</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2490,14 +2588,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130734164</v>
+        <v>130734173</v>
       </c>
       <c r="B17" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2528,10 +2626,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>444362</v>
+        <v>444046</v>
       </c>
       <c r="R17" t="n">
-        <v>7054079</v>
+        <v>7053496</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2568,7 +2666,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På gamla granar.</t>
+          <t>På grenar av en stående död gran med full längd och 36 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2598,12 +2696,12 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2621,14 +2719,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130741317</v>
+        <v>130734174</v>
       </c>
       <c r="B18" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2650,16 +2748,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>443940</v>
+        <v>444078</v>
       </c>
       <c r="R18" t="n">
-        <v>7053078</v>
+        <v>7053449</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2696,7 +2797,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Goda mängder garnlav på flera granar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2705,63 +2806,92 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130741284</v>
+        <v>130734175</v>
       </c>
       <c r="B19" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>443929</v>
+        <v>444124</v>
       </c>
       <c r="R19" t="n">
-        <v>7052944</v>
+        <v>7053447</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2798,7 +2928,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Långväxta bålar på gran.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2807,32 +2937,58 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130734190</v>
+        <v>130734176</v>
       </c>
       <c r="B20" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2863,10 +3019,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>444347</v>
+        <v>444149</v>
       </c>
       <c r="R20" t="n">
-        <v>7053668</v>
+        <v>7053319</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2903,7 +3059,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Garnlav på en stående död gran med full längd och ca 10-20 cm i brösthöjdsdiameter.</t>
+          <t>På gran i gles äldre granskog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2921,11 +3077,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
-        </is>
-      </c>
       <c r="AJ20" t="inlineStr">
         <is>
           <t>gran</t>
@@ -2938,12 +3089,12 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2964,11 +3115,11 @@
         <v>130734177</v>
       </c>
       <c r="B21" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -3092,14 +3243,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130734192</v>
+        <v>130734178</v>
       </c>
       <c r="B22" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -3130,10 +3281,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>444423</v>
+        <v>443988</v>
       </c>
       <c r="R22" t="n">
-        <v>7053773</v>
+        <v>7053189</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3170,7 +3321,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Måttligt till rikligt med garnlavsbålar på flera granar.</t>
+          <t>På gammal gran i luckig äldre granskog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3186,11 +3337,6 @@
       <c r="AH22" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
@@ -3228,41 +3374,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130741314</v>
+        <v>130734179</v>
       </c>
       <c r="B23" t="n">
-        <v>91828</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>444416</v>
+        <v>443901</v>
       </c>
       <c r="R23" t="n">
-        <v>7053728</v>
+        <v>7053212</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3303,59 +3456,81 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>130734150</v>
+        <v>130734180</v>
       </c>
       <c r="B24" t="n">
-        <v>80349</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3363,10 +3538,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>444358</v>
+        <v>443846</v>
       </c>
       <c r="R24" t="n">
-        <v>7054049</v>
+        <v>7053252</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3403,7 +3578,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Gott om bålar av skrovellav på en hyfsat grov sälg.</t>
+          <t>Växer på grenar av en stående död gran med full längd (bhd ca 30 cm).</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3421,29 +3596,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre grandominerad skog med björk och inslag av sälg.</t>
-        </is>
-      </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3461,45 +3631,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>130741297</v>
+        <v>130734181</v>
       </c>
       <c r="B25" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>443871</v>
+        <v>443859</v>
       </c>
       <c r="R25" t="n">
-        <v>7052942</v>
+        <v>7053310</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3536,7 +3709,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gammal gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3545,63 +3718,92 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130741282</v>
+        <v>130734182</v>
       </c>
       <c r="B26" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>443897</v>
+        <v>443903</v>
       </c>
       <c r="R26" t="n">
-        <v>7052981</v>
+        <v>7053286</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3638,7 +3840,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På gran i äldre granskog.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3647,63 +3849,92 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>130741285</v>
+        <v>130734183</v>
       </c>
       <c r="B27" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>443963</v>
+        <v>443986</v>
       </c>
       <c r="R27" t="n">
-        <v>7052972</v>
+        <v>7053263</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3740,7 +3971,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>På gran i gles senvuxen granskog.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3749,32 +3980,63 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Grandominerad skog med björk och inslag av asp.</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>130734162</v>
+        <v>130734184</v>
       </c>
       <c r="B28" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3805,10 +4067,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>444375</v>
+        <v>444032</v>
       </c>
       <c r="R28" t="n">
-        <v>7054118</v>
+        <v>7053290</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3841,6 +4103,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Garnlav på en tydligt gammal gran i gles senvuxen granskog.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3893,14 +4160,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>130734165</v>
+        <v>130734185</v>
       </c>
       <c r="B29" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3931,10 +4198,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>444343</v>
+        <v>444157</v>
       </c>
       <c r="R29" t="n">
-        <v>7054057</v>
+        <v>7053507</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3971,7 +4238,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flera granar.</t>
+          <t>På flera granar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4024,14 +4291,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>130734185</v>
+        <v>130734186</v>
       </c>
       <c r="B30" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -4062,10 +4329,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>444157</v>
+        <v>444272</v>
       </c>
       <c r="R30" t="n">
-        <v>7053507</v>
+        <v>7053547</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4102,7 +4369,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Rikligt med garnlav på flera granar i senvuxen äldre granskog.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4155,41 +4422,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>130741313</v>
+        <v>130734188</v>
       </c>
       <c r="B31" t="n">
-        <v>91828</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr"/>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>443985</v>
+        <v>444304</v>
       </c>
       <c r="R31" t="n">
-        <v>7052983</v>
+        <v>7053564</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4224,77 +4498,103 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Växer på en tydligt gammal gran i relativt senvuxen gles granskog.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>130741290</v>
+        <v>130734189</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>444005</v>
+        <v>444342</v>
       </c>
       <c r="R32" t="n">
-        <v>7053074</v>
+        <v>7053646</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4331,7 +4631,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Bohål ca 3 m upp i granhögstubbe</t>
+          <t>Relativt rikligt med garnlavsbålar på gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4340,32 +4640,63 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>130734181</v>
+        <v>130734190</v>
       </c>
       <c r="B33" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4396,10 +4727,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>443859</v>
+        <v>444347</v>
       </c>
       <c r="R33" t="n">
-        <v>7053310</v>
+        <v>7053668</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4436,7 +4767,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>På gammal gran.</t>
+          <t>Garnlav på en stående död gran med full längd och ca 10-20 cm i brösthöjdsdiameter.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4454,6 +4785,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
+        </is>
+      </c>
       <c r="AJ33" t="inlineStr">
         <is>
           <t>gran</t>
@@ -4466,12 +4802,12 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4489,14 +4825,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>130734178</v>
+        <v>130734191</v>
       </c>
       <c r="B34" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4527,10 +4863,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>443988</v>
+        <v>444407</v>
       </c>
       <c r="R34" t="n">
-        <v>7053189</v>
+        <v>7053726</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4567,7 +4903,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På gammal gran i luckig äldre granskog.</t>
+          <t>Relativt rikligt med garnlav på gran.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4583,6 +4919,11 @@
       <c r="AH34" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ34" t="inlineStr">
@@ -4620,14 +4961,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>130734174</v>
+        <v>130734192</v>
       </c>
       <c r="B35" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4658,10 +4999,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>444078</v>
+        <v>444423</v>
       </c>
       <c r="R35" t="n">
-        <v>7053449</v>
+        <v>7053773</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4698,7 +5039,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Goda mängder garnlav på flera granar.</t>
+          <t>Måttligt till rikligt med garnlavsbålar på flera granar.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4714,6 +5055,11 @@
       <c r="AH35" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
         </is>
       </c>
       <c r="AJ35" t="inlineStr">
@@ -4751,14 +5097,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>130734189</v>
+        <v>130734193</v>
       </c>
       <c r="B36" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4789,10 +5135,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>444342</v>
+        <v>444436</v>
       </c>
       <c r="R36" t="n">
-        <v>7053646</v>
+        <v>7053798</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4825,11 +5171,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med garnlavsbålar på gran.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4887,14 +5228,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>130734176</v>
+        <v>130741316</v>
       </c>
       <c r="B37" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4916,19 +5257,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>444149</v>
+        <v>444000</v>
       </c>
       <c r="R37" t="n">
-        <v>7053319</v>
+        <v>7053558</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4965,7 +5303,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På gran i gles äldre granskog.</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4974,76 +5312,50 @@
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>130741289</v>
+        <v>130741317</v>
       </c>
       <c r="B38" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -5053,10 +5365,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>443999</v>
+        <v>443940</v>
       </c>
       <c r="R38" t="n">
-        <v>7053066</v>
+        <v>7053078</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5093,7 +5405,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5120,32 +5432,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130741294</v>
+        <v>130741318</v>
       </c>
       <c r="B39" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5155,10 +5467,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>443835</v>
+        <v>444153</v>
       </c>
       <c r="R39" t="n">
-        <v>7052933</v>
+        <v>7053487</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5191,11 +5503,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5222,14 +5529,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130741318</v>
+        <v>130741319</v>
       </c>
       <c r="B40" t="n">
-        <v>79243</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -5257,10 +5564,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>444153</v>
+        <v>444417</v>
       </c>
       <c r="R40" t="n">
-        <v>7053487</v>
+        <v>7053741</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5293,6 +5600,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5319,10 +5631,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130734173</v>
+        <v>130734144</v>
       </c>
       <c r="B41" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5330,26 +5642,31 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
@@ -5357,10 +5674,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>444046</v>
+        <v>444016</v>
       </c>
       <c r="R41" t="n">
-        <v>7053496</v>
+        <v>7053579</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5397,7 +5714,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På grenar av en stående död gran med full längd och 36 cm i brösthöjdsdiameter.</t>
+          <t>Ringhack, färska, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5406,7 +5723,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -5427,12 +5743,12 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5450,10 +5766,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130741292</v>
+        <v>130734145</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5479,16 +5795,24 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>443750</v>
+        <v>443967</v>
       </c>
       <c r="R42" t="n">
-        <v>7052993</v>
+        <v>7053469</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5525,7 +5849,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ringhack färska</t>
+          <t>Ringhack, färska och äldre, på stambasen av en gran.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5536,26 +5860,56 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Äldre flerskiktad grandominerad skog.</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130741301</v>
+        <v>130734146</v>
       </c>
       <c r="B43" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5581,16 +5935,24 @@
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>443990</v>
+        <v>443949</v>
       </c>
       <c r="R43" t="n">
-        <v>7052974</v>
+        <v>7053197</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5627,7 +5989,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack, färska, enstaka på stambasen av en gammal gran.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5638,26 +6000,51 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130741295</v>
+        <v>130734147</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5683,16 +6070,24 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>nästsjön, Jmt</t>
+          <t>Henrikmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>443845</v>
+        <v>443820</v>
       </c>
       <c r="R44" t="n">
-        <v>7052918</v>
+        <v>7053223</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5729,7 +6124,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack, färska, i god mängd längs minst 6 meter på en granstam inom en avverkningsanmäld yta och utanför planerad naturhänsyn.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5740,26 +6135,56 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Flerakiktad äldre granskog med björk och inslag av asp. Stor stamdiameterspridning med naturvärdes-granar med över 50 cm i brösthöjdsdiameter.</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130734144</v>
+        <v>130734148</v>
       </c>
       <c r="B45" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5789,7 +6214,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5799,10 +6224,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>444016</v>
+        <v>444153</v>
       </c>
       <c r="R45" t="n">
-        <v>7053579</v>
+        <v>7053496</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5839,7 +6264,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack, färska, på stambasen av en gran.</t>
+          <t>Ringhack, äldre och ev. något färskt, på stambasen av en gran. Medelhögt till högt livsmiljövärde på fyndplatsen baserat på volym stående död ved av gran.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5891,10 +6316,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130741281</v>
+        <v>130741279</v>
       </c>
       <c r="B46" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5926,10 +6351,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>443901</v>
+        <v>444007</v>
       </c>
       <c r="R46" t="n">
-        <v>7053024</v>
+        <v>7053457</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5966,7 +6391,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5993,10 +6418,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130734147</v>
+        <v>130741280</v>
       </c>
       <c r="B47" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6022,24 +6447,16 @@
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>443820</v>
+        <v>444040</v>
       </c>
       <c r="R47" t="n">
-        <v>7053223</v>
+        <v>7053449</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6076,7 +6493,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack, färska, i god mängd längs minst 6 meter på en granstam inom en avverkningsanmäld yta och utanför planerad naturhänsyn.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6087,56 +6504,26 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI47" t="inlineStr">
-        <is>
-          <t>Flerakiktad äldre granskog med björk och inslag av asp. Stor stamdiameterspridning med naturvärdes-granar med över 50 cm i brösthöjdsdiameter.</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130734157</v>
+        <v>130741281</v>
       </c>
       <c r="B48" t="n">
-        <v>91828</v>
+        <v>57953</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6144,37 +6531,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>443945</v>
+        <v>443901</v>
       </c>
       <c r="R48" t="n">
-        <v>7053278</v>
+        <v>7053024</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6211,7 +6595,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i en stående döende gran med full längd i flerskiktad äldre granskog.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6220,54 +6604,28 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130741288</v>
+        <v>130741282</v>
       </c>
       <c r="B49" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6299,10 +6657,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>443996</v>
+        <v>443897</v>
       </c>
       <c r="R49" t="n">
-        <v>7053048</v>
+        <v>7052981</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6339,7 +6697,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6366,10 +6724,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>130741299</v>
+        <v>130741283</v>
       </c>
       <c r="B50" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6401,7 +6759,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>443972</v>
+        <v>443927</v>
       </c>
       <c r="R50" t="n">
         <v>7052967</v>
@@ -6468,10 +6826,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>130734148</v>
+        <v>130741284</v>
       </c>
       <c r="B51" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6497,24 +6855,16 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>444153</v>
+        <v>443929</v>
       </c>
       <c r="R51" t="n">
-        <v>7053496</v>
+        <v>7052944</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6551,7 +6901,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack, äldre och ev. något färskt, på stambasen av en gran. Medelhögt till högt livsmiljövärde på fyndplatsen baserat på volym stående död ved av gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6562,51 +6912,26 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130734146</v>
+        <v>130741285</v>
       </c>
       <c r="B52" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6632,24 +6957,16 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>443949</v>
+        <v>443963</v>
       </c>
       <c r="R52" t="n">
-        <v>7053197</v>
+        <v>7052972</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6686,7 +7003,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ringhack, färska, enstaka på stambasen av en gammal gran.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6697,51 +7014,26 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130734167</v>
+        <v>130741286</v>
       </c>
       <c r="B53" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6749,37 +7041,50 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>444319</v>
+        <v>443968</v>
       </c>
       <c r="R53" t="n">
-        <v>7054017</v>
+        <v>7052990</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6816,7 +7121,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Avbarkade en något klen gran</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6825,54 +7130,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130741316</v>
+        <v>130741287</v>
       </c>
       <c r="B54" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6880,21 +7159,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6907,7 +7186,7 @@
         <v>444000</v>
       </c>
       <c r="R54" t="n">
-        <v>7053558</v>
+        <v>7053028</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6944,7 +7223,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6971,10 +7250,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130741293</v>
+        <v>130741288</v>
       </c>
       <c r="B55" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7006,10 +7285,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>443827</v>
+        <v>443996</v>
       </c>
       <c r="R55" t="n">
-        <v>7052932</v>
+        <v>7053048</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7046,7 +7325,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7073,10 +7352,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130741311</v>
+        <v>130741289</v>
       </c>
       <c r="B56" t="n">
-        <v>91828</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7084,19 +7363,23 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
@@ -7104,10 +7387,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>443991</v>
+        <v>443999</v>
       </c>
       <c r="R56" t="n">
-        <v>7052955</v>
+        <v>7053066</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7140,6 +7423,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7166,10 +7454,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130741310</v>
+        <v>130741290</v>
       </c>
       <c r="B57" t="n">
-        <v>91828</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7177,30 +7465,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>443891</v>
+        <v>444005</v>
       </c>
       <c r="R57" t="n">
-        <v>7053029</v>
+        <v>7053074</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7233,6 +7533,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Bohål ca 3 m upp i granhögstubbe</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7259,10 +7564,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130734171</v>
+        <v>130741291</v>
       </c>
       <c r="B58" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7270,37 +7575,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>443981</v>
+        <v>443794</v>
       </c>
       <c r="R58" t="n">
-        <v>7053488</v>
+        <v>7053002</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7337,7 +7639,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På flera granar.</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7346,54 +7648,28 @@
       <c r="AE58" t="b">
         <v>0</v>
       </c>
-      <c r="AF58" t="inlineStr"/>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130741287</v>
+        <v>130741292</v>
       </c>
       <c r="B59" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7425,10 +7701,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>444000</v>
+        <v>443750</v>
       </c>
       <c r="R59" t="n">
-        <v>7053028</v>
+        <v>7052993</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7465,7 +7741,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7492,10 +7768,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130741298</v>
+        <v>130741293</v>
       </c>
       <c r="B60" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7527,10 +7803,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>443946</v>
+        <v>443827</v>
       </c>
       <c r="R60" t="n">
-        <v>7052921</v>
+        <v>7052932</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7567,7 +7843,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7594,10 +7870,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130741309</v>
+        <v>130741294</v>
       </c>
       <c r="B61" t="n">
-        <v>91828</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7605,19 +7881,23 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
@@ -7625,10 +7905,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>443836</v>
+        <v>443835</v>
       </c>
       <c r="R61" t="n">
-        <v>7052967</v>
+        <v>7052933</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7661,6 +7941,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7687,10 +7972,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>130741308</v>
+        <v>130741295</v>
       </c>
       <c r="B62" t="n">
-        <v>91828</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7698,19 +7983,23 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
@@ -7718,10 +8007,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>444020</v>
+        <v>443845</v>
       </c>
       <c r="R62" t="n">
-        <v>7053458</v>
+        <v>7052918</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7754,6 +8043,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7780,10 +8074,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130741283</v>
+        <v>130741297</v>
       </c>
       <c r="B63" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7815,10 +8109,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>443927</v>
+        <v>443871</v>
       </c>
       <c r="R63" t="n">
-        <v>7052967</v>
+        <v>7052942</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7855,7 +8149,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7882,10 +8176,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130734172</v>
+        <v>130741298</v>
       </c>
       <c r="B64" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7893,37 +8187,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>444002</v>
+        <v>443946</v>
       </c>
       <c r="R64" t="n">
-        <v>7053503</v>
+        <v>7052921</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7958,60 +8249,39 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130734179</v>
+        <v>130741299</v>
       </c>
       <c r="B65" t="n">
-        <v>79243</v>
+        <v>57953</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8019,37 +8289,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>443901</v>
+        <v>443972</v>
       </c>
       <c r="R65" t="n">
-        <v>7053212</v>
+        <v>7052967</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8084,60 +8351,39 @@
           <t>2026-01-16</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130734155</v>
+        <v>130741301</v>
       </c>
       <c r="B66" t="n">
-        <v>91804</v>
+        <v>57953</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8145,41 +8391,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>443861</v>
+        <v>443990</v>
       </c>
       <c r="R66" t="n">
-        <v>7053306</v>
+        <v>7052974</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8216,7 +8455,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Flera fruktkroppar i stambasen av en levande relativt grov gran.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8225,54 +8464,28 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130734151</v>
+        <v>130741302</v>
       </c>
       <c r="B67" t="n">
-        <v>80349</v>
+        <v>57953</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8280,37 +8493,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Henrikmyren, Jmt</t>
+          <t>nästsjön, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>444218</v>
+        <v>443997</v>
       </c>
       <c r="R67" t="n">
-        <v>7053557</v>
+        <v>7053008</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8347,7 +8557,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Växer på en levande skadad sälg.</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8356,945 +8566,21 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI67" t="inlineStr">
-        <is>
-          <t>Flerskiktad äldre granskog med inslag av björk och enstaka sälg.</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>130741280</v>
-      </c>
-      <c r="B68" t="n">
-        <v>57884</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>nästsjön, Jmt</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>444040</v>
-      </c>
-      <c r="R68" t="n">
-        <v>7053449</v>
-      </c>
-      <c r="S68" t="n">
-        <v>10</v>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U68" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V68" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y68" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AA68" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
-        </is>
-      </c>
-      <c r="AD68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG68" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT68" t="inlineStr"/>
-      <c r="AW68" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>130734184</v>
-      </c>
-      <c r="B69" t="n">
-        <v>79243</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Henrikmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>444032</v>
-      </c>
-      <c r="R69" t="n">
-        <v>7053290</v>
-      </c>
-      <c r="S69" t="n">
-        <v>10</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Garnlav på en tydligt gammal gran i gles senvuxen granskog.</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>130734188</v>
-      </c>
-      <c r="B70" t="n">
-        <v>79243</v>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>Henrikmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>444304</v>
-      </c>
-      <c r="R70" t="n">
-        <v>7053564</v>
-      </c>
-      <c r="S70" t="n">
-        <v>10</v>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V70" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W70" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y70" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AA70" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Växer på en tydligt gammal gran i relativt senvuxen gles granskog.</t>
-        </is>
-      </c>
-      <c r="AD70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF70" t="inlineStr"/>
-      <c r="AG70" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT70" t="inlineStr"/>
-      <c r="AW70" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY70" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>130734191</v>
-      </c>
-      <c r="B71" t="n">
-        <v>79243</v>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E71" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>Henrikmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>444407</v>
-      </c>
-      <c r="R71" t="n">
-        <v>7053726</v>
-      </c>
-      <c r="S71" t="n">
-        <v>10</v>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V71" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W71" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y71" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AA71" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Relativt rikligt med garnlav på gran.</t>
-        </is>
-      </c>
-      <c r="AD71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF71" t="inlineStr"/>
-      <c r="AG71" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI71" t="inlineStr">
-        <is>
-          <t>Äldre flerskiktad grandominerad skog med björk och inslag av sälg.</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT71" t="inlineStr"/>
-      <c r="AW71" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY71" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>130734168</v>
-      </c>
-      <c r="B72" t="n">
-        <v>79243</v>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E72" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>Henrikmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>444293</v>
-      </c>
-      <c r="R72" t="n">
-        <v>7054016</v>
-      </c>
-      <c r="S72" t="n">
-        <v>10</v>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V72" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W72" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AD72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF72" t="inlineStr"/>
-      <c r="AG72" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT72" t="inlineStr"/>
-      <c r="AW72" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY72" t="inlineStr"/>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>130734169</v>
-      </c>
-      <c r="B73" t="n">
-        <v>79243</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E73" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>Henrikmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>444160</v>
-      </c>
-      <c r="R73" t="n">
-        <v>7053858</v>
-      </c>
-      <c r="S73" t="n">
-        <v>10</v>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V73" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W73" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på gran.</t>
-        </is>
-      </c>
-      <c r="AD73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF73" t="inlineStr"/>
-      <c r="AG73" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT73" t="inlineStr"/>
-      <c r="AW73" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>130734183</v>
-      </c>
-      <c r="B74" t="n">
-        <v>79243</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E74" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>Henrikmyren, Jmt</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>443986</v>
-      </c>
-      <c r="R74" t="n">
-        <v>7053263</v>
-      </c>
-      <c r="S74" t="n">
-        <v>10</v>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U74" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V74" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W74" t="inlineStr">
-        <is>
-          <t>Offerdal</t>
-        </is>
-      </c>
-      <c r="Y74" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AA74" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På gran i gles senvuxen granskog.</t>
-        </is>
-      </c>
-      <c r="AD74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF74" t="inlineStr"/>
-      <c r="AG74" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI74" t="inlineStr">
-        <is>
-          <t>Grandominerad skog med björk och inslag av asp.</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
-      </c>
-      <c r="AT74" t="inlineStr"/>
-      <c r="AW74" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61382-2025 artfynd.xlsx
+++ b/artfynd/A 61382-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY67"/>
+  <dimension ref="A1:AZ67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741320</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734153</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1044,6 +1059,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734155</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1184,6 +1204,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734150</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1320,6 +1345,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734151</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1426,6 +1456,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113995171</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1552,6 +1587,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734162</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1683,6 +1723,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734164</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1814,6 +1859,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734165</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1945,6 +1995,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734167</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2071,6 +2126,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734168</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2202,6 +2262,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734169</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2328,6 +2393,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734170</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2459,6 +2529,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734171</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2585,6 +2660,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734172</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2716,6 +2796,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734173</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2847,6 +2932,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734174</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2978,6 +3068,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734175</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3109,6 +3204,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734176</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3240,6 +3340,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734177</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3371,6 +3476,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734178</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3497,6 +3607,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734179</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3628,6 +3743,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734180</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3759,6 +3879,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734181</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3890,6 +4015,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734182</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4026,6 +4156,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734183</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4157,6 +4292,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734184</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4288,6 +4428,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734185</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4419,6 +4564,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734186</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4550,6 +4700,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734188</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4686,6 +4841,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734189</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4822,6 +4982,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734190</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4958,6 +5123,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734191</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5094,6 +5264,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734192</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5225,6 +5400,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734193</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5327,6 +5507,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741316</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5429,6 +5614,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741317</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5526,6 +5716,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741318</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5628,6 +5823,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741319</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5763,6 +5963,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734144</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5903,6 +6108,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734145</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6038,6 +6248,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734146</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6178,6 +6393,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734147</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6313,6 +6533,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130734148</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6415,6 +6640,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741279</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6517,6 +6747,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741280</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6619,6 +6854,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741281</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6721,6 +6961,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741282</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6823,6 +7068,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741283</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6925,6 +7175,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741284</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7027,6 +7282,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741285</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7145,6 +7405,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741286</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7247,6 +7512,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741287</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7349,6 +7619,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741288</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7451,6 +7726,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741289</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7561,6 +7841,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741290</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7663,6 +7948,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741291</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7765,6 +8055,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741292</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7867,6 +8162,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741293</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7969,6 +8269,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741294</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8071,6 +8376,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741295</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8173,6 +8483,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741297</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8275,6 +8590,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741298</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8377,6 +8697,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741299</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8479,6 +8804,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741301</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8581,8 +8911,81 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130741302</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>